--- a/transport/transport_data.xlsx
+++ b/transport/transport_data.xlsx
@@ -452,7 +452,7 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>ФАКТУРА_НОМЕР</t>
+          <t>ЛИТРИ_1</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
@@ -462,7 +462,7 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>ИНФОРМАЦИЯ</t>
+          <t>ЛИТРИ_2</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
@@ -2130,10 +2130,8 @@
           <t>НЕПЛАТЕНА</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>1 евро на км за малък камион - иска фиксиран транспорт 90 евро - СУ Никола Вапцаров + КРЗ Одесос</t>
-        </is>
+      <c r="P20" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2552,11 +2550,6 @@
           <t>НЕПЛАТЕНА</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>градски курс</t>
-        </is>
-      </c>
       <c r="T25" t="inlineStr">
         <is>
           <t>Simeon Hadzhiev</t>
@@ -4472,10 +4465,8 @@
           <t>НЕПЛАТЕНА</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>транспорт на км 1,10евро без ДДС</t>
-        </is>
+      <c r="P47" s="2" t="n">
+        <v>110</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6577,10 +6568,8 @@
           <t>НЕПЛАТЕНА</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Повишен транспорт - по 1евро на км без ДДС</t>
-        </is>
+      <c r="P71" s="2" t="n">
+        <v>-1</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7636,11 +7625,6 @@
           <t>НЕПЛАТЕНА</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>Офис София</t>
-        </is>
-      </c>
       <c r="Q83" s="3" t="n">
         <v>8.09</v>
       </c>
@@ -7733,11 +7717,6 @@
           <t>НЕПЛАТЕНА</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Офис София</t>
-        </is>
-      </c>
       <c r="Q84" s="3" t="n">
         <v>4.66</v>
       </c>
@@ -7829,11 +7808,6 @@
           <t>НЕПЛАТЕНА</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Офис София</t>
-        </is>
-      </c>
       <c r="Q85" s="3" t="n">
         <v>35.01</v>
       </c>
@@ -7925,11 +7899,6 @@
           <t>НЕПЛАТЕНА</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Офис София</t>
-        </is>
-      </c>
       <c r="T86" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
@@ -8018,11 +7987,6 @@
           <t>НЕПЛАТЕНА</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Офис София</t>
-        </is>
-      </c>
       <c r="T87" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
@@ -8111,11 +8075,6 @@
           <t>НЕПЛАТЕНА</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>Офис София</t>
-        </is>
-      </c>
       <c r="T88" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
@@ -8204,11 +8163,6 @@
           <t>НЕПЛАТЕНА</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>Офис София</t>
-        </is>
-      </c>
       <c r="T89" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
@@ -8297,11 +8251,6 @@
           <t>НЕПЛАТЕНА</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>Офис София</t>
-        </is>
-      </c>
       <c r="T90" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
@@ -8390,11 +8339,6 @@
           <t>НЕПЛАТЕНА</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>Офис София</t>
-        </is>
-      </c>
       <c r="T91" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
@@ -8483,11 +8427,6 @@
           <t>НЕПЛАТЕНА</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>Офис София</t>
-        </is>
-      </c>
       <c r="T92" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
@@ -8576,11 +8515,6 @@
           <t>НЕПЛАТЕНА</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>Офис София</t>
-        </is>
-      </c>
       <c r="T93" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
@@ -8669,11 +8603,6 @@
           <t>НЕПЛАТЕНА</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>Офис София</t>
-        </is>
-      </c>
       <c r="T94" t="inlineStr">
         <is>
           <t>Vesela Nikolova</t>
@@ -14266,10 +14195,8 @@
           <t>НЕПЛАТЕНА</t>
         </is>
       </c>
-      <c r="P155" t="inlineStr">
-        <is>
-          <t>9500</t>
-        </is>
+      <c r="P155" s="2" t="n">
+        <v>9500</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -14364,10 +14291,8 @@
           <t>НЕПЛАТЕНА</t>
         </is>
       </c>
-      <c r="P156" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
+      <c r="P156" s="2" t="n">
+        <v>6000</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -14465,10 +14390,8 @@
           <t>НЕПЛАТЕНА</t>
         </is>
       </c>
-      <c r="P157" t="inlineStr">
-        <is>
-          <t>20000</t>
-        </is>
+      <c r="P157" s="2" t="n">
+        <v>20000</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -14518,7 +14441,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Варна-Повеляново-Тервел-Варна</t>
+          <t>Варна-НХК-Повеляново-Тервел-Варна</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14563,10 +14486,8 @@
           <t>НЕПЛАТЕНА</t>
         </is>
       </c>
-      <c r="P158" t="inlineStr">
-        <is>
-          <t>30000</t>
-        </is>
+      <c r="P158" s="2" t="n">
+        <v>30000</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -14582,7 +14503,7 @@
         </is>
       </c>
       <c r="W158" s="4" t="n">
-        <v>46175.7166493287</v>
+        <v>46184.62743337963</v>
       </c>
       <c r="X158" t="inlineStr">
         <is>
@@ -14597,6 +14518,3486 @@
       <c r="Z158" t="inlineStr">
         <is>
           <t>02</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="19.2" customHeight="1">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>20260611-0001</t>
+        </is>
+      </c>
+      <c r="B159" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Каварна-Ген.Колево-Добрич-Повеляново-Варна</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>520</v>
+      </c>
+      <c r="K159" s="2" t="n">
+        <v>30500</v>
+      </c>
+      <c r="L159" s="2" t="n">
+        <v>624</v>
+      </c>
+      <c r="M159" s="3" t="n">
+        <v>20.45901639344262</v>
+      </c>
+      <c r="N159" s="2" t="n">
+        <v>12500</v>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P159" s="2" t="n">
+        <v>17500</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U159" s="4" t="n">
+        <v>46184.62754288194</v>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W159" s="4" t="n">
+        <v>46184.63027123843</v>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="19.2" customHeight="1">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>20260611-0002</t>
+        </is>
+      </c>
+      <c r="B160" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Варна-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="K160" s="2" t="n">
+        <v>17000</v>
+      </c>
+      <c r="L160" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="M160" s="3" t="n">
+        <v>9.176470588235295</v>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P160" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U160" s="4" t="n">
+        <v>46184.63038962963</v>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W160" s="4" t="n">
+        <v>46184.63267920139</v>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="19.2" customHeight="1">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>20260611-0003</t>
+        </is>
+      </c>
+      <c r="B161" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Варна-Повелново-Девня-Каварна-Варна</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="K161" s="2" t="n">
+        <v>27000</v>
+      </c>
+      <c r="L161" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="M161" s="3" t="n">
+        <v>8.888888888888889</v>
+      </c>
+      <c r="N161" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P161" s="2" t="n">
+        <v>21000</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U161" s="4" t="n">
+        <v>46184.63273450232</v>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W161" s="4" t="n">
+        <v>46184.63524068287</v>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="19.2" customHeight="1">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>20260611-0004</t>
+        </is>
+      </c>
+      <c r="B162" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Варна-Ботево-Добрич-Генерал Киселово-Метличина-Провадия</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="K162" s="2" t="n">
+        <v>31000</v>
+      </c>
+      <c r="L162" s="2" t="n">
+        <v>288</v>
+      </c>
+      <c r="M162" s="3" t="n">
+        <v>9.29032258064516</v>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P162" s="2" t="n">
+        <v>19500</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U162" s="4" t="n">
+        <v>46184.63482149305</v>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W162" s="4" t="n">
+        <v>46184.63773777778</v>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="19.2" customHeight="1">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>20260611-0005</t>
+        </is>
+      </c>
+      <c r="B163" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Варна-Добич-Варна</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="K163" s="2" t="n">
+        <v>24200</v>
+      </c>
+      <c r="L163" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="M163" s="3" t="n">
+        <v>6.446280991735537</v>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U163" s="4" t="n">
+        <v>46184.63780768518</v>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W163" s="4" t="n">
+        <v>46184.63873554398</v>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="19.2" customHeight="1">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>20260611-0006</t>
+        </is>
+      </c>
+      <c r="B164" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Русе-Кладенци-Тервел-Карапелит-Русе</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="n">
+        <v>370</v>
+      </c>
+      <c r="K164" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L164" s="2" t="n">
+        <v>444</v>
+      </c>
+      <c r="M164" s="3" t="n">
+        <v>13.875</v>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P164" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U164" s="4" t="n">
+        <v>46184.63880133102</v>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W164" s="4" t="n">
+        <v>46184.64068787037</v>
+      </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="19.2" customHeight="1">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>20260611-0007</t>
+        </is>
+      </c>
+      <c r="B165" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Слънчев бряг-Каварна-Малина-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="K165" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L165" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="M165" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="N165" s="2" t="n">
+        <v>11000</v>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P165" s="2" t="n">
+        <v>14500</v>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U165" s="4" t="n">
+        <v>46184.64074501157</v>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W165" s="4" t="n">
+        <v>46184.64307834491</v>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="19.2" customHeight="1">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>20260611-0008</t>
+        </is>
+      </c>
+      <c r="B166" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Варна-КРЗ-Енево-Повеляново-Варна</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="K166" s="2" t="n">
+        <v>16600</v>
+      </c>
+      <c r="L166" s="2" t="n">
+        <v>204</v>
+      </c>
+      <c r="M166" s="3" t="n">
+        <v>12.28915662650602</v>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P166" s="2" t="n">
+        <v>16600</v>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U166" s="4" t="n">
+        <v>46184.64312028935</v>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W166" s="4" t="n">
+        <v>46184.64638982639</v>
+      </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="19.2" customHeight="1">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>20260611-0009</t>
+        </is>
+      </c>
+      <c r="B167" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Варна-Добрич-Черна-Тополи-Варна</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="K167" s="2" t="n">
+        <v>32500</v>
+      </c>
+      <c r="L167" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="M167" s="3" t="n">
+        <v>7.384615384615384</v>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P167" s="2" t="n">
+        <v>9000</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U167" s="4" t="n">
+        <v>46184.64833924769</v>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W167" s="4" t="n">
+        <v>46184.65177487268</v>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="19.2" customHeight="1">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>20260611-0010</t>
+        </is>
+      </c>
+      <c r="B168" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Варна-Каварна-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="K168" s="2" t="n">
+        <v>22000</v>
+      </c>
+      <c r="L168" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="M168" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N168" s="2" t="n">
+        <v>8000</v>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P168" s="2" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U168" s="4" t="n">
+        <v>46184.64954732639</v>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W168" s="4" t="n">
+        <v>46184.65310967593</v>
+      </c>
+      <c r="X168" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="19.2" customHeight="1">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>20260622-0001</t>
+        </is>
+      </c>
+      <c r="B169" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Русе-Тервел-Гешаново-НХК</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="K169" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L169" s="2" t="n">
+        <v>420</v>
+      </c>
+      <c r="M169" s="3" t="n">
+        <v>13.125</v>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P169" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U169" s="4" t="n">
+        <v>46195.38174271991</v>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W169" s="4" t="n">
+        <v>46195.43283659723</v>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="19.2" customHeight="1">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>20260622-0002</t>
+        </is>
+      </c>
+      <c r="B170" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Летище Бургас</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="K170" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="M170" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U170" s="4" t="n">
+        <v>46195.38726195602</v>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W170" s="4" t="n">
+        <v>46195.38853579861</v>
+      </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="19.2" customHeight="1">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>20260622-0003</t>
+        </is>
+      </c>
+      <c r="B171" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>НХК-Пчелник-Повеляново-Девня-Енево-Аспарухово</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="K171" s="2" t="n">
+        <v>16000</v>
+      </c>
+      <c r="L171" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="M171" s="3" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P171" s="2" t="n">
+        <v>7000</v>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U171" s="4" t="n">
+        <v>46195.38863185185</v>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W171" s="4" t="n">
+        <v>46195.4332097338</v>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="19.2" customHeight="1">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>20260622-0004</t>
+        </is>
+      </c>
+      <c r="B172" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Аспарухово - Бяла-Русе</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="n">
+        <v>230</v>
+      </c>
+      <c r="K172" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L172" s="2" t="n">
+        <v>276</v>
+      </c>
+      <c r="M172" s="3" t="n">
+        <v>8.625</v>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U172" s="4" t="n">
+        <v>46195.39231096065</v>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W172" s="4" t="n">
+        <v>46195.39337960648</v>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="19.2" customHeight="1">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>20260622-0005</t>
+        </is>
+      </c>
+      <c r="B173" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Каварна-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="n">
+        <v>470</v>
+      </c>
+      <c r="K173" s="2" t="n">
+        <v>31000</v>
+      </c>
+      <c r="L173" s="2" t="n">
+        <v>564</v>
+      </c>
+      <c r="M173" s="3" t="n">
+        <v>18.19354838709678</v>
+      </c>
+      <c r="N173" s="2" t="n">
+        <v>19500</v>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P173" s="2" t="n">
+        <v>21500</v>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U173" s="4" t="n">
+        <v>46195.39341222222</v>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W173" s="4" t="n">
+        <v>46195.43477030093</v>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="19.2" customHeight="1">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>20260622-0006</t>
+        </is>
+      </c>
+      <c r="B174" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Варна-Девня-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="K174" s="2" t="n">
+        <v>29000</v>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>204</v>
+      </c>
+      <c r="M174" s="3" t="n">
+        <v>7.03448275862069</v>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P174" s="2" t="n">
+        <v>7000</v>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U174" s="4" t="n">
+        <v>46195.39610645833</v>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W174" s="4" t="n">
+        <v>46195.43517862268</v>
+      </c>
+      <c r="X174" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="19.2" customHeight="1">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>20260622-0007</t>
+        </is>
+      </c>
+      <c r="B175" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Варна-Пчелник-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="K175" s="2" t="n">
+        <v>31000</v>
+      </c>
+      <c r="L175" s="2" t="n">
+        <v>540</v>
+      </c>
+      <c r="M175" s="3" t="n">
+        <v>17.41935483870968</v>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P175" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U175" s="4" t="n">
+        <v>46195.39974881944</v>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W175" s="4" t="n">
+        <v>46195.43539539352</v>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="19.2" customHeight="1">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>20260622-0008</t>
+        </is>
+      </c>
+      <c r="B176" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Русе-Силистра-Тервел-Карапелит- Островче-Ушинци-Русе</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="K176" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L176" s="2" t="n">
+        <v>480</v>
+      </c>
+      <c r="M176" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P176" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U176" s="4" t="n">
+        <v>46195.40310622686</v>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W176" s="4" t="n">
+        <v>46195.43617247685</v>
+      </c>
+      <c r="X176" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="19.2" customHeight="1">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>20260622-0009</t>
+        </is>
+      </c>
+      <c r="B177" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Варна-Долни Чифлик-Аспарухово- Дългопол-Невша-Енево-Брестак-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="K177" s="2" t="n">
+        <v>28000</v>
+      </c>
+      <c r="L177" s="2" t="n">
+        <v>384</v>
+      </c>
+      <c r="M177" s="3" t="n">
+        <v>13.71428571428571</v>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P177" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U177" s="4" t="n">
+        <v>46195.40646696759</v>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W177" s="4" t="n">
+        <v>46195.43605405092</v>
+      </c>
+      <c r="X177" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="19.2" customHeight="1">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>20260622-0010</t>
+        </is>
+      </c>
+      <c r="B178" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Варна-Девня-Повеляново-Белослав-Варна</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="K178" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L178" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="M178" s="3" t="n">
+        <v>4.277777777777778</v>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P178" s="2" t="n">
+        <v>17400</v>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U178" s="4" t="n">
+        <v>46195.4103290162</v>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W178" s="4" t="n">
+        <v>46195.43639299768</v>
+      </c>
+      <c r="X178" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="19.2" customHeight="1">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>20260622-0011</t>
+        </is>
+      </c>
+      <c r="B179" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Варна-Хидрострой-Варна</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="K179" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L179" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="M179" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P179" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U179" s="4" t="n">
+        <v>46195.41254501158</v>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W179" s="4" t="n">
+        <v>46195.43645275463</v>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="19.2" customHeight="1">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>20260624-0001</t>
+        </is>
+      </c>
+      <c r="B180" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Русе-Ушинци-Подайва-Нова Камена-Тервел-Русе</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="K180" s="2" t="n">
+        <v>28000</v>
+      </c>
+      <c r="L180" s="2" t="n">
+        <v>480</v>
+      </c>
+      <c r="M180" s="3" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P180" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U180" s="4" t="n">
+        <v>46197.72570414352</v>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W180" s="4" t="n">
+        <v>46197.73334074074</v>
+      </c>
+      <c r="X180" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="19.2" customHeight="1">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>20260624-0002</t>
+        </is>
+      </c>
+      <c r="B181" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Енево-Вълчи дол-Северняк-Ген.Тошево-Варна</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="n">
+        <v>420</v>
+      </c>
+      <c r="K181" s="2" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L181" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="M181" s="3" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P181" s="2" t="n">
+        <v>16000</v>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U181" s="4" t="n">
+        <v>46197.72746626157</v>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W181" s="4" t="n">
+        <v>46197.73395716435</v>
+      </c>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="19.2" customHeight="1">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>20260624-0003</t>
+        </is>
+      </c>
+      <c r="B182" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Варна-Каварна-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="K182" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L182" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="M182" s="3" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="N182" s="2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P182" s="2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U182" s="4" t="n">
+        <v>46197.72995211805</v>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W182" s="4" t="n">
+        <v>46197.73480944445</v>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="19.2" customHeight="1">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>20260624-0004</t>
+        </is>
+      </c>
+      <c r="B183" s="1" t="n">
+        <v>46198</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Илиянци-Пещерна-Илиянци</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Маг Трейд-2016 ЕООД</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>ДИМИТЪР ПЪРВАНОВ БОРИСОВ</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>СВ5138ЕО</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="K183" s="2" t="n">
+        <v>18400</v>
+      </c>
+      <c r="L183" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="M183" s="3" t="n">
+        <v>10.32608695652174</v>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P183" s="2" t="n">
+        <v>18400</v>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U183" s="4" t="n">
+        <v>46197.73136142361</v>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W183" s="4" t="n">
+        <v>46197.73491296297</v>
+      </c>
+      <c r="X183" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="19.2" customHeight="1">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>20260624-0005</t>
+        </is>
+      </c>
+      <c r="B184" s="1" t="n">
+        <v>46198</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Каварна-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="n">
+        <v>470</v>
+      </c>
+      <c r="K184" s="2" t="n">
+        <v>31000</v>
+      </c>
+      <c r="L184" s="2" t="n">
+        <v>564</v>
+      </c>
+      <c r="M184" s="3" t="n">
+        <v>18.19354838709678</v>
+      </c>
+      <c r="N184" s="2" t="n">
+        <v>13000</v>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P184" s="2" t="n">
+        <v>13000</v>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U184" s="4" t="n">
+        <v>46197.73499663195</v>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W184" s="4" t="n">
+        <v>46197.74079207176</v>
+      </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="19.2" customHeight="1">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>20260624-0006</t>
+        </is>
+      </c>
+      <c r="B185" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Русе-Тервел-Русе</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>P2849EE</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="K185" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L185" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="M185" s="3" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P185" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U185" s="4" t="n">
+        <v>46197.7362227199</v>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W185" s="4" t="n">
+        <v>46197.74061559028</v>
+      </c>
+      <c r="X185" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="19.2" customHeight="1">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>20260624-0007</t>
+        </is>
+      </c>
+      <c r="B186" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Снежина-Доброплодно-есеница-Вълчи дол-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="K186" s="2" t="n">
+        <v>35000</v>
+      </c>
+      <c r="L186" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="M186" s="3" t="n">
+        <v>10.28571428571428</v>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P186" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U186" s="4" t="n">
+        <v>46197.73770605324</v>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W186" s="4" t="n">
+        <v>46198.66709708334</v>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="19.2" customHeight="1">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>20260624-0008</t>
+        </is>
+      </c>
+      <c r="B187" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Курс външен 109 бензин от НХК Скорпио</t>
+        </is>
+      </c>
+      <c r="K187" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L187" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="M187" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P187" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U187" s="4" t="n">
+        <v>46197.74101706019</v>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W187" s="4" t="n">
+        <v>46197.74152724537</v>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="19.2" customHeight="1">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>20260624-0009</t>
+        </is>
+      </c>
+      <c r="B188" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>НХК-Деветак-Невестино-Нова Бяла Река-НХК</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>СТАНИСЛАВ ДИМИТРОВ ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>А1535ВВ</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="K188" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L188" s="2" t="n">
+        <v>265</v>
+      </c>
+      <c r="M188" s="3" t="n">
+        <v>14.72222222222222</v>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P188" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U188" s="4" t="n">
+        <v>46197.74160743056</v>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W188" s="4" t="n">
+        <v>46198.66654521991</v>
+      </c>
+      <c r="X188" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="19.2" customHeight="1">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>20260625-0001</t>
+        </is>
+      </c>
+      <c r="B189" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Варна-Хидро-Варна</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="K189" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L189" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="M189" s="3" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P189" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U189" s="4" t="n">
+        <v>46198.66364039352</v>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W189" s="4" t="n">
+        <v>46198.67138862269</v>
+      </c>
+      <c r="X189" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="19.2" customHeight="1">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>20260625-0002</t>
+        </is>
+      </c>
+      <c r="B190" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Варна-Повеляново-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="K190" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L190" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="M190" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P190" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U190" s="4" t="n">
+        <v>46198.66902997685</v>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W190" s="4" t="n">
+        <v>46198.67155340278</v>
+      </c>
+      <c r="X190" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="19.2" customHeight="1">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>20260706-0001</t>
+        </is>
+      </c>
+      <c r="B191" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Варна-Каварна-Добрич-Варна-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>B7902TM</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="n">
+        <v>310</v>
+      </c>
+      <c r="K191" s="2" t="n">
+        <v>35000</v>
+      </c>
+      <c r="M191" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N191" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P191" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U191" s="4" t="n">
+        <v>46209.64720302083</v>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W191" s="4" t="n">
+        <v>46209.64904087963</v>
+      </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="19.2" customHeight="1">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>20260706-0002</t>
+        </is>
+      </c>
+      <c r="B192" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Варна-ПБ Аспарухово-Тервел-Салс-Варна</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="K192" s="2" t="n">
+        <v>31000</v>
+      </c>
+      <c r="L192" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="M192" s="3" t="n">
+        <v>11.61290322580645</v>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P192" s="2" t="n">
+        <v>30500</v>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U192" s="4" t="n">
+        <v>46209.65221041667</v>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W192" s="4" t="n">
+        <v>46209.65873082176</v>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="19.2" customHeight="1">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>20260706-0003</t>
+        </is>
+      </c>
+      <c r="B193" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>курс Външен Осем ви от НХК</t>
+        </is>
+      </c>
+      <c r="K193" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L193" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="M193" s="3" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P193" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U193" s="4" t="n">
+        <v>46209.65254587963</v>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W193" s="4" t="n">
+        <v>46209.65808215278</v>
+      </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="19.2" customHeight="1">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>20260706-0004</t>
+        </is>
+      </c>
+      <c r="B194" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Балкан</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K194" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L194" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="M194" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P194" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U194" s="4" t="n">
+        <v>46209.65892913195</v>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W194" s="4" t="n">
+        <v>46209.65984548611</v>
+      </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="19.2" customHeight="1">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>20260706-0005</t>
+        </is>
+      </c>
+      <c r="B195" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Дългопол-Долни Чифлик</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>"СИ-ТРАНС БЪЛГАРИЯ"  ЕООД</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Живко Демиров Вълчев</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>В9261РА</t>
+        </is>
+      </c>
+      <c r="K195" s="2" t="n">
+        <v>11000</v>
+      </c>
+      <c r="L195" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="M195" s="3" t="n">
+        <v>14.63636363636364</v>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P195" s="2" t="n">
+        <v>11000</v>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U195" s="4" t="n">
+        <v>46209.66029009259</v>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W195" s="4" t="n">
+        <v>46209.67772440972</v>
+      </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>06</t>
         </is>
       </c>
     </row>

--- a/transport/transport_data.xlsx
+++ b/transport/transport_data.xlsx
@@ -18001,6 +18001,5783 @@
         </is>
       </c>
     </row>
+    <row r="196" ht="19.2" customHeight="1">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>20260713-0001</t>
+        </is>
+      </c>
+      <c r="B196" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Варна-Вълчи дол-Брестак- Карапелит -Близнаци-Енево-Варна</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="K196" s="2" t="n">
+        <v>30500</v>
+      </c>
+      <c r="L196" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="M196" s="3" t="n">
+        <v>11.80327868852459</v>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P196" s="2" t="n">
+        <v>30500</v>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U196" s="4" t="n">
+        <v>46216.49319362269</v>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W196" s="4" t="n">
+        <v>46216.49627605324</v>
+      </c>
+      <c r="X196" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="19.2" customHeight="1">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>20260713-0002</t>
+        </is>
+      </c>
+      <c r="B197" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Варна - НХК- Каварна-Ген. Тошево -Добрич-Ген Киселово -Варна</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J197" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="K197" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L197" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="M197" s="3" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="N197" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P197" s="2" t="n">
+        <v>27000</v>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U197" s="4" t="n">
+        <v>46216.49638982639</v>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W197" s="4" t="n">
+        <v>46216.50103082176</v>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="19.2" customHeight="1">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>20260713-0003</t>
+        </is>
+      </c>
+      <c r="B198" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>НХК - Деветак - ДЕН -НХК</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>ДИРОСИ ООД</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>СТАНИСЛАВ ДИМИТРОВ ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>А5420НХ</t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="K198" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L198" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="M198" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P198" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U198" s="4" t="n">
+        <v>46216.50406953703</v>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W198" s="4" t="n">
+        <v>46216.50729239584</v>
+      </c>
+      <c r="X198" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="19.2" customHeight="1">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>20260713-0004</t>
+        </is>
+      </c>
+      <c r="B199" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Варна-Хидро-Варна</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>B7902TM</t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="K199" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L199" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="M199" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P199" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U199" s="4" t="n">
+        <v>46216.50734398148</v>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W199" s="4" t="n">
+        <v>46216.5124669213</v>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="19.2" customHeight="1">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>20260713-0005</t>
+        </is>
+      </c>
+      <c r="B200" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Русе-Мартен-Снежина-Блъсково-Русе</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>ДИНАС ТРЕЙДИНГ ООД</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>ТОДОР ДИМИТРОВ ПОПОВ</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>ОВ7977ВА</t>
+        </is>
+      </c>
+      <c r="J200" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="K200" s="2" t="n">
+        <v>18700</v>
+      </c>
+      <c r="L200" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="M200" s="3" t="n">
+        <v>15.02673796791444</v>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P200" s="2" t="n">
+        <v>18700</v>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U200" s="4" t="n">
+        <v>46216.50879719907</v>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W200" s="4" t="n">
+        <v>46216.51254923611</v>
+      </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="19.2" customHeight="1">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>20260713-0006</t>
+        </is>
+      </c>
+      <c r="B201" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Варна-Енево-Дългопол-Неново-Варна</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J201" s="2" t="n">
+        <v>230</v>
+      </c>
+      <c r="K201" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L201" s="2" t="n">
+        <v>276</v>
+      </c>
+      <c r="M201" s="3" t="n">
+        <v>8.625</v>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P201" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U201" s="4" t="n">
+        <v>46216.51203040509</v>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W201" s="4" t="n">
+        <v>46226.72711627315</v>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="19.2" customHeight="1">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>20260723-0001</t>
+        </is>
+      </c>
+      <c r="B202" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Русе-Тервел-Карапелит-Енево-Русе</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>P2849EE</t>
+        </is>
+      </c>
+      <c r="J202" s="2" t="n">
+        <v>380</v>
+      </c>
+      <c r="K202" s="2" t="n">
+        <v>32500</v>
+      </c>
+      <c r="L202" s="2" t="n">
+        <v>456</v>
+      </c>
+      <c r="M202" s="3" t="n">
+        <v>14.03076923076923</v>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P202" s="2" t="n">
+        <v>32500</v>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U202" s="4" t="n">
+        <v>46226.72457708333</v>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W202" s="4" t="n">
+        <v>46226.72692784722</v>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="19.2" customHeight="1">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>20260723-0002</t>
+        </is>
+      </c>
+      <c r="B203" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Варна-Добрич-Каварна-Варна</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>B7902TM</t>
+        </is>
+      </c>
+      <c r="J203" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="K203" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L203" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="M203" s="3" t="n">
+        <v>10.55555555555556</v>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P203" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U203" s="4" t="n">
+        <v>46226.72717081018</v>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W203" s="4" t="n">
+        <v>46226.73598834491</v>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="19.2" customHeight="1">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>20260723-0003</t>
+        </is>
+      </c>
+      <c r="B204" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>НХК-Невестино-Нова Бяла Река- НХК</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>ДИРОСИ ООД</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>СТАНИСЛАВ ДИМИТРОВ ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>А5420НХ</t>
+        </is>
+      </c>
+      <c r="J204" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="K204" s="2" t="n">
+        <v>11500</v>
+      </c>
+      <c r="L204" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="M204" s="3" t="n">
+        <v>18.08695652173913</v>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P204" s="2" t="n">
+        <v>11500</v>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U204" s="4" t="n">
+        <v>46226.73601989583</v>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W204" s="4" t="n">
+        <v>46226.74483497685</v>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="19.2" customHeight="1">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>20260723-0004</t>
+        </is>
+      </c>
+      <c r="B205" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Варна - Аспарухово - Ген. Киселово - Тр. Март - Атаасов - Стожер - Варна</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J205" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="K205" s="2" t="n">
+        <v>35000</v>
+      </c>
+      <c r="L205" s="2" t="n">
+        <v>294</v>
+      </c>
+      <c r="M205" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P205" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U205" s="4" t="n">
+        <v>46226.74488517361</v>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W205" s="4" t="n">
+        <v>46226.75744288194</v>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="19.2" customHeight="1">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>20260723-0005</t>
+        </is>
+      </c>
+      <c r="B206" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Варна-Нефтохим-Каварна-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J206" s="2" t="n">
+        <v>470</v>
+      </c>
+      <c r="K206" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L206" s="2" t="n">
+        <v>564</v>
+      </c>
+      <c r="M206" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="N206" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P206" s="2" t="n">
+        <v>24000</v>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U206" s="4" t="n">
+        <v>46226.747060625</v>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W206" s="4" t="n">
+        <v>46226.75699377315</v>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="19.2" customHeight="1">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>20260723-0006</t>
+        </is>
+      </c>
+      <c r="B207" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Варна-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="J207" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="K207" s="2" t="n">
+        <v>19800</v>
+      </c>
+      <c r="L207" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="M207" s="3" t="n">
+        <v>7.777777777777778</v>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U207" s="4" t="n">
+        <v>46226.75654454861</v>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W207" s="4" t="n">
+        <v>46226.75922252315</v>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="19.2" customHeight="1">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>20260723-0007</t>
+        </is>
+      </c>
+      <c r="B208" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Варна- Паскалево - Брестак- Ведрина -Девня - Варна</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="J208" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="K208" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L208" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="M208" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P208" s="2" t="n">
+        <v>8700</v>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U208" s="4" t="n">
+        <v>46226.75936627315</v>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W208" s="4" t="n">
+        <v>46226.76167126157</v>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="19.2" customHeight="1">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>20260723-0008</t>
+        </is>
+      </c>
+      <c r="B209" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Русе - Тервел- Ушинци- Островче-Русе</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>P2849EE</t>
+        </is>
+      </c>
+      <c r="J209" s="2" t="n">
+        <v>370</v>
+      </c>
+      <c r="K209" s="2" t="n">
+        <v>32200</v>
+      </c>
+      <c r="L209" s="2" t="n">
+        <v>444</v>
+      </c>
+      <c r="M209" s="3" t="n">
+        <v>13.7888198757764</v>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P209" s="2" t="n">
+        <v>32200</v>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U209" s="4" t="n">
+        <v>46226.76172083333</v>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W209" s="4" t="n">
+        <v>46226.76360349537</v>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="19.2" customHeight="1">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>20260723-0009</t>
+        </is>
+      </c>
+      <c r="B210" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Варна-лайт - Любен-Вълчи дол-Доброплодно-Терем - Варна</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>B7902TM</t>
+        </is>
+      </c>
+      <c r="J210" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="K210" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L210" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="M210" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P210" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U210" s="4" t="n">
+        <v>46226.76418998843</v>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W210" s="4" t="n">
+        <v>46226.76583188657</v>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="19.2" customHeight="1">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>20260723-0010</t>
+        </is>
+      </c>
+      <c r="B211" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Варна-109-балкан-Варна</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="J211" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="K211" s="2" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L211" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="M211" s="3" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="N211" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P211" s="2" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U211" s="4" t="n">
+        <v>46226.76587137731</v>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W211" s="4" t="n">
+        <v>46226.76769857639</v>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="19.2" customHeight="1">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>20260723-0011</t>
+        </is>
+      </c>
+      <c r="B212" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Варна-Калиманци -Генерал Тошво-Каварна-Варна</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="J212" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="K212" s="2" t="n">
+        <v>20100</v>
+      </c>
+      <c r="L212" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="M212" s="3" t="n">
+        <v>10.9452736318408</v>
+      </c>
+      <c r="N212" s="2" t="n">
+        <v>11600</v>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P212" s="2" t="n">
+        <v>20100</v>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U212" s="4" t="n">
+        <v>46226.76774040509</v>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W212" s="4" t="n">
+        <v>46226.76937555555</v>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="19.2" customHeight="1">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>20260723-0012</t>
+        </is>
+      </c>
+      <c r="B213" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Русе-Снеежина-Блъсково</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>ЕЛ-ПЛАМ ТРАНС ЕООД</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>МИЛЕН БОРИСОВ ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Р0202КМ</t>
+        </is>
+      </c>
+      <c r="J213" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="K213" s="2" t="n">
+        <v>17600</v>
+      </c>
+      <c r="L213" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="M213" s="3" t="n">
+        <v>15.96590909090909</v>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P213" s="2" t="n">
+        <v>17600</v>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U213" s="4" t="n">
+        <v>46226.76944221065</v>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W213" s="4" t="n">
+        <v>46226.77241523148</v>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="19.2" customHeight="1">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>20260723-0013</t>
+        </is>
+      </c>
+      <c r="B214" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Блъсково-Лукойл Аспарухово - Провадия - Тервел</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>ЕЛ-ПЛАМ ТРАНС ЕООД</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>МИЛЕН БОРИСОВ ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Р0202КМ</t>
+        </is>
+      </c>
+      <c r="J214" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="K214" s="2" t="n">
+        <v>18600</v>
+      </c>
+      <c r="L214" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="M214" s="3" t="n">
+        <v>11.88172043010753</v>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P214" s="2" t="n">
+        <v>18600</v>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U214" s="4" t="n">
+        <v>46226.77307825231</v>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W214" s="4" t="n">
+        <v>46226.77434431713</v>
+      </c>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="19.2" customHeight="1">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>20260723-0014</t>
+        </is>
+      </c>
+      <c r="B215" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Варна-Добрич-Вълчи дол-Любен-Варна</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>B7902TM</t>
+        </is>
+      </c>
+      <c r="J215" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="K215" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L215" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="M215" s="3" t="n">
+        <v>8.888888888888889</v>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P215" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U215" s="4" t="n">
+        <v>46226.7760040625</v>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W215" s="4" t="n">
+        <v>46226.77723466435</v>
+      </c>
+      <c r="X215" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="19.2" customHeight="1">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>20260723-0015</t>
+        </is>
+      </c>
+      <c r="B216" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>НХК-Деветак-Ден-нов-НХК</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>РОСБУЛ ТРАНС</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>МИЛЕН СТЕФАНОВ АНДРЕЕВ</t>
+        </is>
+      </c>
+      <c r="J216" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="K216" s="2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L216" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="M216" s="3" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P216" s="2" t="n">
+        <v>7000</v>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U216" s="4" t="n">
+        <v>46226.77727359954</v>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W216" s="4" t="n">
+        <v>46226.77845359954</v>
+      </c>
+      <c r="X216" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="19.2" customHeight="1">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>20260723-0016</t>
+        </is>
+      </c>
+      <c r="B217" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Варна-ПБ Аспарухово -Долни Чифлик -Малина-Преселенци-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>B7902TM</t>
+        </is>
+      </c>
+      <c r="J217" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="K217" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L217" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="M217" s="3" t="n">
+        <v>18.33333333333333</v>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P217" s="2" t="n">
+        <v>7000</v>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U217" s="4" t="n">
+        <v>46226.77857734953</v>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W217" s="4" t="n">
+        <v>46226.78067006944</v>
+      </c>
+      <c r="X217" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="19.2" customHeight="1">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>20260727-0001</t>
+        </is>
+      </c>
+      <c r="B218" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Варна-Каварна-Топливо-Варна</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>B7902TM</t>
+        </is>
+      </c>
+      <c r="J218" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="K218" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L218" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="M218" s="3" t="n">
+        <v>10.55555555555556</v>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P218" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U218" s="4" t="n">
+        <v>46230.71050601852</v>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W218" s="4" t="n">
+        <v>46230.71205414352</v>
+      </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="19.2" customHeight="1">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>20260727-0002</t>
+        </is>
+      </c>
+      <c r="B219" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>НХК-Долни Чифлик- Повеляново-Стожер-Добрич-Карапелит-Тервел-Окорш-Подайва-Русе</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J219" s="2" t="n">
+        <v>430</v>
+      </c>
+      <c r="K219" s="2" t="n">
+        <v>33000</v>
+      </c>
+      <c r="L219" s="2" t="n">
+        <v>516</v>
+      </c>
+      <c r="M219" s="3" t="n">
+        <v>15.63636363636363</v>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P219" s="2" t="n">
+        <v>25000</v>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U219" s="4" t="n">
+        <v>46230.71209068287</v>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W219" s="4" t="n">
+        <v>46230.71719895834</v>
+      </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="19.2" customHeight="1">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>20260727-0003</t>
+        </is>
+      </c>
+      <c r="B220" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>НХК-Слъчнев-НХК</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>ДИРОСИ ООД</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>СТАНИСЛАВ ДИМИТРОВ ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>А1535ВВ</t>
+        </is>
+      </c>
+      <c r="J220" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="K220" s="2" t="n">
+        <v>3500</v>
+      </c>
+      <c r="L220" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="M220" s="3" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U220" s="4" t="n">
+        <v>46230.71724793981</v>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W220" s="4" t="n">
+        <v>46230.71814626158</v>
+      </c>
+      <c r="X220" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="19.2" customHeight="1">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>20260727-0004</t>
+        </is>
+      </c>
+      <c r="B221" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Варна-Белфери-Варна</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="J221" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K221" s="2" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L221" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="M221" s="3" t="n">
+        <v>6.875</v>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P221" s="2" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U221" s="4" t="n">
+        <v>46230.7182065625</v>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W221" s="4" t="n">
+        <v>46230.71974243056</v>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="19.2" customHeight="1">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>20260727-0005</t>
+        </is>
+      </c>
+      <c r="B222" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Варна-Хидро-Варна</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Р4961ЕЕ</t>
+        </is>
+      </c>
+      <c r="J222" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="K222" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L222" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="M222" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P222" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U222" s="4" t="n">
+        <v>46230.71977907408</v>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W222" s="4" t="n">
+        <v>46230.72071596065</v>
+      </c>
+      <c r="X222" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="19.2" customHeight="1">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>20260727-0006</t>
+        </is>
+      </c>
+      <c r="B223" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Илиянци - Аетомаг - Илиянци</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>ЕТ  Латеви 3</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>АТАНАС ЛАТЕВ</t>
+        </is>
+      </c>
+      <c r="K223" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M223" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P223" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U223" s="4" t="n">
+        <v>46230.72074798611</v>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W223" s="4" t="n">
+        <v>46230.72171193287</v>
+      </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="19.2" customHeight="1">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>20260727-0007</t>
+        </is>
+      </c>
+      <c r="B224" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Русе-Ушинци-Енево-Риш-Бяла река-Нова Бяла река-НХК</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J224" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="K224" s="2" t="n">
+        <v>22000</v>
+      </c>
+      <c r="L224" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="M224" s="3" t="n">
+        <v>18.18181818181818</v>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P224" s="2" t="n">
+        <v>22000</v>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U224" s="4" t="n">
+        <v>46230.72174629629</v>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W224" s="4" t="n">
+        <v>46230.7267715162</v>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="19.2" customHeight="1">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>20260727-0008</t>
+        </is>
+      </c>
+      <c r="B225" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Варна-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J225" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K225" s="2" t="n">
+        <v>13500</v>
+      </c>
+      <c r="L225" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="M225" s="3" t="n">
+        <v>8.148148148148147</v>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P225" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U225" s="4" t="n">
+        <v>46230.72708842593</v>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W225" s="4" t="n">
+        <v>46230.74156783565</v>
+      </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="19.2" customHeight="1">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>20260727-0009</t>
+        </is>
+      </c>
+      <c r="B226" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Варна-Лукойл Аспарухво- Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J226" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="K226" s="2" t="n">
+        <v>32300</v>
+      </c>
+      <c r="L226" s="2" t="n">
+        <v>384</v>
+      </c>
+      <c r="M226" s="3" t="n">
+        <v>11.88854489164087</v>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P226" s="2" t="n">
+        <v>10300</v>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U226" s="4" t="n">
+        <v>46230.74160552083</v>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W226" s="4" t="n">
+        <v>46230.74638886574</v>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="19.2" customHeight="1">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>20260727-0010</t>
+        </is>
+      </c>
+      <c r="B227" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Варна-каварна-ЗПЗ-Варна</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>B7902TM</t>
+        </is>
+      </c>
+      <c r="J227" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="K227" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="L227" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="M227" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P227" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U227" s="4" t="n">
+        <v>46230.74520458333</v>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W227" s="4" t="n">
+        <v>46230.74683976852</v>
+      </c>
+      <c r="X227" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="19.2" customHeight="1">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>20260727-0011</t>
+        </is>
+      </c>
+      <c r="B228" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Варна-Лукойл Аспарухово-Тервел-Нова Камена- Повеляново-Варна</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J228" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="K228" s="2" t="n">
+        <v>34000</v>
+      </c>
+      <c r="L228" s="2" t="n">
+        <v>384</v>
+      </c>
+      <c r="M228" s="3" t="n">
+        <v>11.29411764705882</v>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P228" s="2" t="n">
+        <v>34000</v>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U228" s="4" t="n">
+        <v>46230.74687325231</v>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W228" s="4" t="n">
+        <v>46230.74907175926</v>
+      </c>
+      <c r="X228" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="19.2" customHeight="1">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>20260727-0012</t>
+        </is>
+      </c>
+      <c r="B229" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Каварна-Добрич-Повеляново-Варна</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J229" s="2" t="n">
+        <v>490</v>
+      </c>
+      <c r="K229" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L229" s="2" t="n">
+        <v>588</v>
+      </c>
+      <c r="M229" s="3" t="n">
+        <v>18.375</v>
+      </c>
+      <c r="N229" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P229" s="2" t="n">
+        <v>21000</v>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U229" s="4" t="n">
+        <v>46230.74917895834</v>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W229" s="4" t="n">
+        <v>46230.75137488426</v>
+      </c>
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="19.2" customHeight="1">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>20260727-0013</t>
+        </is>
+      </c>
+      <c r="B230" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>НХК-Дългопол-Блъсково-Енево-Тервел-Русе</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>P2849EE</t>
+        </is>
+      </c>
+      <c r="J230" s="2" t="n">
+        <v>380</v>
+      </c>
+      <c r="K230" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L230" s="2" t="n">
+        <v>456</v>
+      </c>
+      <c r="M230" s="3" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P230" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U230" s="4" t="n">
+        <v>46230.75142952547</v>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W230" s="4" t="n">
+        <v>46230.76296365741</v>
+      </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z230" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="19.2" customHeight="1">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>20260727-0014</t>
+        </is>
+      </c>
+      <c r="B231" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Варна-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>B7902TM</t>
+        </is>
+      </c>
+      <c r="J231" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="K231" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L231" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="M231" s="3" t="n">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U231" s="4" t="n">
+        <v>46230.76300325232</v>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W231" s="4" t="n">
+        <v>46230.7642481713</v>
+      </c>
+      <c r="X231" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="19.2" customHeight="1">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>20260727-0015</t>
+        </is>
+      </c>
+      <c r="B232" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Варна-Кипра-Варна</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>B7902TM</t>
+        </is>
+      </c>
+      <c r="J232" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="K232" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L232" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="M232" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P232" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U232" s="4" t="n">
+        <v>46230.76433818287</v>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W232" s="4" t="n">
+        <v>46230.76541332176</v>
+      </c>
+      <c r="X232" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="19.2" customHeight="1">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>20260727-0016</t>
+        </is>
+      </c>
+      <c r="B233" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Неново-Кладенци-Нова Камена-Тервел-Брестак-Ботево-Варна</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J233" s="2" t="n">
+        <v>370</v>
+      </c>
+      <c r="K233" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L233" s="2" t="n">
+        <v>444</v>
+      </c>
+      <c r="M233" s="3" t="n">
+        <v>13.875</v>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P233" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U233" s="4" t="n">
+        <v>46230.76545769676</v>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W233" s="4" t="n">
+        <v>46230.76754228009</v>
+      </c>
+      <c r="X233" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="19.2" customHeight="1">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>20260727-0017</t>
+        </is>
+      </c>
+      <c r="B234" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>НХК-Тервел-Нова Камена-Русе</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J234" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="K234" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L234" s="2" t="n">
+        <v>480</v>
+      </c>
+      <c r="M234" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P234" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U234" s="4" t="n">
+        <v>46230.76758295139</v>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W234" s="4" t="n">
+        <v>46230.76934679398</v>
+      </c>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="19.2" customHeight="1">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>20260727-0018</t>
+        </is>
+      </c>
+      <c r="B235" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Варна-Тополи-Варна</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J235" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="K235" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L235" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="M235" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P235" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U235" s="4" t="n">
+        <v>46230.76943574074</v>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W235" s="4" t="n">
+        <v>46230.77017958333</v>
+      </c>
+      <c r="X235" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="19.2" customHeight="1">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>20260727-0019</t>
+        </is>
+      </c>
+      <c r="B236" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Варна-Паскалево-Добрич-Малина-Вълччи дол-Карапелит-Повелчново-Варна</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J236" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="K236" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L236" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="M236" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P236" s="2" t="n">
+        <v>20700</v>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U236" s="4" t="n">
+        <v>46230.77021915509</v>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W236" s="4" t="n">
+        <v>46230.77286944444</v>
+      </c>
+      <c r="X236" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="19.2" customHeight="1">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>20260727-0020</t>
+        </is>
+      </c>
+      <c r="B237" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Каварна-Генерал Тошево-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J237" s="2" t="n">
+        <v>530</v>
+      </c>
+      <c r="K237" s="2" t="n">
+        <v>30500</v>
+      </c>
+      <c r="L237" s="2" t="n">
+        <v>252</v>
+      </c>
+      <c r="M237" s="3" t="n">
+        <v>8.262295081967213</v>
+      </c>
+      <c r="N237" s="2" t="n">
+        <v>16300</v>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P237" s="2" t="n">
+        <v>30500</v>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U237" s="4" t="n">
+        <v>46230.77290387732</v>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W237" s="4" t="n">
+        <v>46230.77869033565</v>
+      </c>
+      <c r="X237" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y237" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z237" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="19.2" customHeight="1">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>20260727-0021</t>
+        </is>
+      </c>
+      <c r="B238" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Варна-Добрич-девня-Повеляново-Варна</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J238" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="K238" s="2" t="n">
+        <v>36100</v>
+      </c>
+      <c r="L238" s="2" t="n">
+        <v>204</v>
+      </c>
+      <c r="M238" s="3" t="n">
+        <v>5.650969529085873</v>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P238" s="2" t="n">
+        <v>8100</v>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U238" s="4" t="n">
+        <v>46230.77490055555</v>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W238" s="4" t="n">
+        <v>46230.77651741898</v>
+      </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="19.2" customHeight="1">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>20260727-0022</t>
+        </is>
+      </c>
+      <c r="B239" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Илиянци-Орешец-Илиянци</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>ЕТ  Латеви 3</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>АТАНАС ЛАТЕВ</t>
+        </is>
+      </c>
+      <c r="J239" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="K239" s="2" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M239" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P239" s="2" t="n">
+        <v>3500</v>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U239" s="4" t="n">
+        <v>46230.77626702546</v>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W239" s="4" t="n">
+        <v>46230.77744115741</v>
+      </c>
+      <c r="X239" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="19.2" customHeight="1">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>20260727-0023</t>
+        </is>
+      </c>
+      <c r="B240" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>НХК-Каблешково-Слънчев бряг-НХК</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>ДИРОСИ ООД</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>СТАНИСЛАВ ДИМИТРОВ ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="J240" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="K240" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L240" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="M240" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P240" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U240" s="4" t="n">
+        <v>46230.77747502315</v>
+      </c>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W240" s="4" t="n">
+        <v>46230.77957065972</v>
+      </c>
+      <c r="X240" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y240" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z240" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="19.2" customHeight="1">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>20260727-0024</t>
+        </is>
+      </c>
+      <c r="B241" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>НХК-Тервел-Подайва-Островче-Русе</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J241" s="2" t="n">
+        <v>430</v>
+      </c>
+      <c r="K241" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L241" s="2" t="n">
+        <v>520</v>
+      </c>
+      <c r="M241" s="3" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P241" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U241" s="4" t="n">
+        <v>46230.77961247685</v>
+      </c>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W241" s="4" t="n">
+        <v>46230.78126341435</v>
+      </c>
+      <c r="X241" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y241" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z241" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="19.2" customHeight="1">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>20260727-0025</t>
+        </is>
+      </c>
+      <c r="B242" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Варна-Добрич-Черна-Жегларци-Вълчи дол-Варна</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J242" s="2" t="n">
+        <v>510</v>
+      </c>
+      <c r="K242" s="2" t="n">
+        <v>30500</v>
+      </c>
+      <c r="L242" s="2" t="n">
+        <v>612</v>
+      </c>
+      <c r="M242" s="3" t="n">
+        <v>20.0655737704918</v>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P242" s="2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U242" s="4" t="n">
+        <v>46230.78129653935</v>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W242" s="4" t="n">
+        <v>46230.78438060185</v>
+      </c>
+      <c r="X242" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="19.2" customHeight="1">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>20260727-0026</t>
+        </is>
+      </c>
+      <c r="B243" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Варна-Тополи-Варна</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>"СИ-ТРАНС БЪЛГАРИЯ"  ЕООД</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Живко Демиров Вълчев</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>В9296ТМ</t>
+        </is>
+      </c>
+      <c r="J243" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="K243" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L243" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="M243" s="3" t="n">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P243" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U243" s="4" t="n">
+        <v>46230.78444726852</v>
+      </c>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W243" s="4" t="n">
+        <v>46233.30296422454</v>
+      </c>
+      <c r="X243" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y243" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z243" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="19.2" customHeight="1">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>20260727-0027</t>
+        </is>
+      </c>
+      <c r="B244" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Долни Чифлик-Повелново-Варна</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J244" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="K244" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L244" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="M244" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="N244" s="2" t="n">
+        <v>23500</v>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P244" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U244" s="4" t="n">
+        <v>46230.78623402778</v>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W244" s="4" t="n">
+        <v>46230.78765055555</v>
+      </c>
+      <c r="X244" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="19.2" customHeight="1">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>20260727-0028</t>
+        </is>
+      </c>
+      <c r="B245" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Русе-Нова Камена-Безмер-Тервел-Стефан Караджа-Русе</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J245" s="2" t="n">
+        <v>380</v>
+      </c>
+      <c r="K245" s="2" t="n">
+        <v>33000</v>
+      </c>
+      <c r="L245" s="2" t="n">
+        <v>456</v>
+      </c>
+      <c r="M245" s="3" t="n">
+        <v>13.81818181818182</v>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P245" s="2" t="n">
+        <v>33000</v>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U245" s="4" t="n">
+        <v>46230.78768533565</v>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W245" s="4" t="n">
+        <v>46230.78972136574</v>
+      </c>
+      <c r="X245" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="19.2" customHeight="1">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>20260727-0029</t>
+        </is>
+      </c>
+      <c r="B246" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Варна-Любен-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>B7902TM</t>
+        </is>
+      </c>
+      <c r="J246" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="K246" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L246" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="M246" s="3" t="n">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P246" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U246" s="4" t="n">
+        <v>46230.78987251157</v>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W246" s="4" t="n">
+        <v>46230.79082233796</v>
+      </c>
+      <c r="X246" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="19.2" customHeight="1">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>20260727-0030</t>
+        </is>
+      </c>
+      <c r="B247" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Девня-Варна</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J247" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="K247" s="2" t="n">
+        <v>31200</v>
+      </c>
+      <c r="L247" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="M247" s="3" t="n">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P247" s="2" t="n">
+        <v>31200</v>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U247" s="4" t="n">
+        <v>46230.79086861111</v>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W247" s="4" t="n">
+        <v>46230.79244086806</v>
+      </c>
+      <c r="X247" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="19.2" customHeight="1">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>20260727-0031</t>
+        </is>
+      </c>
+      <c r="B248" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Варна-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>B7902TM</t>
+        </is>
+      </c>
+      <c r="J248" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="K248" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L248" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="M248" s="3" t="n">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U248" s="4" t="n">
+        <v>46230.7925642824</v>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W248" s="4" t="n">
+        <v>46232.56315938658</v>
+      </c>
+      <c r="X248" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="19.2" customHeight="1">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>20260729-0001</t>
+        </is>
+      </c>
+      <c r="B249" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>109 с Живко</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>"СИ-ТРАНС БЪЛГАРИЯ"  ЕООД</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Живко Демиров Вълчев</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>В9296ТМ</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>В6351ЕН</t>
+        </is>
+      </c>
+      <c r="K249" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L249" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="M249" s="3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P249" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U249" s="4" t="n">
+        <v>46232.56324780093</v>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W249" s="4" t="n">
+        <v>46232.56432777778</v>
+      </c>
+      <c r="X249" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="19.2" customHeight="1">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>20260729-0002</t>
+        </is>
+      </c>
+      <c r="B250" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Варна-Осем ви - Вълчи дол-Варна</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J250" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="K250" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L250" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="M250" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P250" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U250" s="4" t="n">
+        <v>46232.56404</v>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W250" s="4" t="n">
+        <v>46232.60665849537</v>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="19.2" customHeight="1">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>20260729-0003</t>
+        </is>
+      </c>
+      <c r="B251" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Каварна-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J251" s="2" t="n">
+        <v>460</v>
+      </c>
+      <c r="K251" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L251" s="2" t="n">
+        <v>552</v>
+      </c>
+      <c r="M251" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="N251" s="2" t="n">
+        <v>18500</v>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P251" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U251" s="4" t="n">
+        <v>46232.60669181713</v>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W251" s="4" t="n">
+        <v>46233.41310152777</v>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="19.2" customHeight="1">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>20260729-0004</t>
+        </is>
+      </c>
+      <c r="B252" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Русе-Снежина-Русе</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>ДИНАС ТРЕЙДИНГ ООД</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Теодор Александров Георгиев</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>ОВ7977ВА</t>
+        </is>
+      </c>
+      <c r="J252" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="K252" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="L252" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="M252" s="3" t="n">
+        <v>10.93333333333333</v>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P252" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U252" s="4" t="n">
+        <v>46232.61734944444</v>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W252" s="4" t="n">
+        <v>46233.3412196875</v>
+      </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="19.2" customHeight="1">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>20260730-0001</t>
+        </is>
+      </c>
+      <c r="B253" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Повеляново-Варна</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J253" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="K253" s="2" t="n">
+        <v>35000</v>
+      </c>
+      <c r="L253" s="2" t="n">
+        <v>288</v>
+      </c>
+      <c r="M253" s="3" t="n">
+        <v>8.22857142857143</v>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P253" s="2" t="n">
+        <v>35000</v>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U253" s="4" t="n">
+        <v>46233.34104105324</v>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W253" s="4" t="n">
+        <v>46233.68732106481</v>
+      </c>
+      <c r="X253" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y253" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z253" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="19.2" customHeight="1">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>20260730-0002</t>
+        </is>
+      </c>
+      <c r="B254" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Варна-Дългопол-Варна</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>B7902TM</t>
+        </is>
+      </c>
+      <c r="J254" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K254" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L254" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M254" s="3" t="n">
+        <v>16.66666666666667</v>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P254" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U254" s="4" t="n">
+        <v>46233.34351690972</v>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W254" s="4" t="n">
+        <v>46233.40626489584</v>
+      </c>
+      <c r="X254" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="19.2" customHeight="1">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>20260730-0003</t>
+        </is>
+      </c>
+      <c r="B255" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Русе-Тервел-Карапелит-Добрич-Русе</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J255" s="2" t="n">
+        <v>420</v>
+      </c>
+      <c r="K255" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L255" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="M255" s="3" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P255" s="2" t="n">
+        <v>24000</v>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U255" s="4" t="n">
+        <v>46233.4093446412</v>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W255" s="4" t="n">
+        <v>46233.41085193287</v>
+      </c>
+      <c r="X255" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="19.2" customHeight="1">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>20260730-0004</t>
+        </is>
+      </c>
+      <c r="B256" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>НХК-Пчелник-Добрич-Тервел-Русе</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="J256" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="K256" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L256" s="2" t="n">
+        <v>540</v>
+      </c>
+      <c r="M256" s="3" t="n">
+        <v>16.875</v>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P256" s="2" t="n">
+        <v>4500</v>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U256" s="4" t="n">
+        <v>46233.4110431713</v>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W256" s="4" t="n">
+        <v>46233.41279827547</v>
+      </c>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="19.2" customHeight="1">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>20260730-0005</t>
+        </is>
+      </c>
+      <c r="B257" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Варна-Хидро-Варна</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J257" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="K257" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L257" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="M257" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P257" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U257" s="4" t="n">
+        <v>46233.41344859954</v>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W257" s="4" t="n">
+        <v>46233.41439766204</v>
+      </c>
+      <c r="X257" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/transport/transport_data.xlsx
+++ b/transport/transport_data.xlsx
@@ -20912,16 +20912,16 @@
         </is>
       </c>
       <c r="J227" s="2" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="K227" s="2" t="n">
         <v>15000</v>
       </c>
       <c r="L227" s="2" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="M227" s="3" t="n">
-        <v>10</v>
+        <v>11.33333333333333</v>
       </c>
       <c r="O227" t="inlineStr">
         <is>
@@ -20945,7 +20945,7 @@
         </is>
       </c>
       <c r="W227" s="4" t="n">
-        <v>46230.74683976852</v>
+        <v>46237.71828126157</v>
       </c>
       <c r="X227" t="inlineStr">
         <is>
@@ -23775,6 +23775,4768 @@
       <c r="Z257" t="inlineStr">
         <is>
           <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="19.2" customHeight="1">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>20260806-0001</t>
+        </is>
+      </c>
+      <c r="B258" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Варна-Бяла-Варна</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J258" s="2" t="n">
+        <v>420</v>
+      </c>
+      <c r="K258" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L258" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="M258" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U258" s="4" t="n">
+        <v>46240.73343105324</v>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W258" s="4" t="n">
+        <v>46240.73788818287</v>
+      </c>
+      <c r="X258" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z258" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="19.2" customHeight="1">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>20260806-0002</t>
+        </is>
+      </c>
+      <c r="B259" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Бяла-Русе-Тервел-Гешаново-Близнаци-Русе</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="J259" s="2" t="n">
+        <v>440</v>
+      </c>
+      <c r="K259" s="2" t="n">
+        <v>31000</v>
+      </c>
+      <c r="L259" s="2" t="n">
+        <v>528</v>
+      </c>
+      <c r="M259" s="3" t="n">
+        <v>17.03225806451613</v>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P259" s="2" t="n">
+        <v>31000</v>
+      </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U259" s="4" t="n">
+        <v>46240.73796966435</v>
+      </c>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W259" s="4" t="n">
+        <v>46240.73968159722</v>
+      </c>
+      <c r="X259" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y259" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z259" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="19.2" customHeight="1">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>20260806-0003</t>
+        </is>
+      </c>
+      <c r="B260" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Бяла-Русе-Варна-Добрич-Русе</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J260" s="2" t="n">
+        <v>570</v>
+      </c>
+      <c r="K260" s="2" t="n">
+        <v>34000</v>
+      </c>
+      <c r="L260" s="2" t="n">
+        <v>684</v>
+      </c>
+      <c r="M260" s="3" t="n">
+        <v>20.11764705882353</v>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P260" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U260" s="4" t="n">
+        <v>46240.73971719907</v>
+      </c>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W260" s="4" t="n">
+        <v>46240.74147510417</v>
+      </c>
+      <c r="X260" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y260" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z260" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="19.2" customHeight="1">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>20260806-0004</t>
+        </is>
+      </c>
+      <c r="B261" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Каварна-Добрич-Повеляново-Терем-Варна</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J261" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="K261" s="2" t="n">
+        <v>31000</v>
+      </c>
+      <c r="L261" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="M261" s="3" t="n">
+        <v>19.35483870967742</v>
+      </c>
+      <c r="N261" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P261" s="2" t="n">
+        <v>23000</v>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U261" s="4" t="n">
+        <v>46240.74150913194</v>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W261" s="4" t="n">
+        <v>46240.7443197338</v>
+      </c>
+      <c r="X261" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y261" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="19.2" customHeight="1">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>20260806-0005</t>
+        </is>
+      </c>
+      <c r="B262" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Бяла-Русе-Нова камена-Тервел-Карапелит-Русе</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="J262" s="2" t="n">
+        <v>430</v>
+      </c>
+      <c r="K262" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L262" s="2" t="n">
+        <v>516</v>
+      </c>
+      <c r="M262" s="3" t="n">
+        <v>16.125</v>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P262" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U262" s="4" t="n">
+        <v>46240.74437995371</v>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W262" s="4" t="n">
+        <v>46240.74647008102</v>
+      </c>
+      <c r="X262" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y262" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="19.2" customHeight="1">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>20260806-0006</t>
+        </is>
+      </c>
+      <c r="B263" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Аспарухово-Бяла-Шумен-Вълчи дол-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>"СИ-ТРАНС БЪЛГАРИЯ"  ЕООД</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Живко Демиров Вълчев</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>В9261РА</t>
+        </is>
+      </c>
+      <c r="J263" s="2" t="n">
+        <v>485</v>
+      </c>
+      <c r="K263" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L263" s="2" t="n">
+        <v>510</v>
+      </c>
+      <c r="M263" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P263" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U263" s="4" t="n">
+        <v>46240.74650496527</v>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W263" s="4" t="n">
+        <v>46241.46184988426</v>
+      </c>
+      <c r="X263" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y263" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z263" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="19.2" customHeight="1">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>20260806-0007</t>
+        </is>
+      </c>
+      <c r="B264" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Варна-Девня-Повеляново-Осем ви-Аспарухово-Варна</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J264" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="K264" s="2" t="n">
+        <v>26000</v>
+      </c>
+      <c r="L264" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="M264" s="3" t="n">
+        <v>9.230769230769232</v>
+      </c>
+      <c r="N264" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P264" s="2" t="n">
+        <v>29000</v>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U264" s="4" t="n">
+        <v>46240.75203077546</v>
+      </c>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W264" s="4" t="n">
+        <v>46240.75517672454</v>
+      </c>
+      <c r="X264" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y264" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z264" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="19.2" customHeight="1">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>20260806-0008</t>
+        </is>
+      </c>
+      <c r="B265" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Русе-бяла-Пчелник-Варна</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J265" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="K265" s="2" t="n">
+        <v>16000</v>
+      </c>
+      <c r="L265" s="2" t="n">
+        <v>348</v>
+      </c>
+      <c r="M265" s="3" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U265" s="4" t="n">
+        <v>46240.7552682176</v>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W265" s="4" t="n">
+        <v>46240.75634476852</v>
+      </c>
+      <c r="X265" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y265" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="19.2" customHeight="1">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>20260806-0009</t>
+        </is>
+      </c>
+      <c r="B266" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Каварна-Малина-Гешаново-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J266" s="2" t="n">
+        <v>480</v>
+      </c>
+      <c r="K266" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L266" s="2" t="n">
+        <v>576</v>
+      </c>
+      <c r="M266" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="N266" s="2" t="n">
+        <v>21000</v>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P266" s="2" t="n">
+        <v>24000</v>
+      </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U266" s="4" t="n">
+        <v>46240.7564490625</v>
+      </c>
+      <c r="V266" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W266" s="4" t="n">
+        <v>46240.75857275463</v>
+      </c>
+      <c r="X266" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y266" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z266" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="19.2" customHeight="1">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>20260806-0010</t>
+        </is>
+      </c>
+      <c r="B267" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>НХК-Чайка-Астер-Калина-Арсена-НХК</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>ДИРОСИ ООД</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>СТАНИСЛАВ ДИМИТРОВ ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>А1535ВВ</t>
+        </is>
+      </c>
+      <c r="J267" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="K267" s="2" t="n">
+        <v>6500</v>
+      </c>
+      <c r="L267" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="M267" s="3" t="n">
+        <v>20.76923076923077</v>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U267" s="4" t="n">
+        <v>46240.75861923611</v>
+      </c>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W267" s="4" t="n">
+        <v>46240.7596140625</v>
+      </c>
+      <c r="X267" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y267" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z267" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="19.2" customHeight="1">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>20260806-0011</t>
+        </is>
+      </c>
+      <c r="B268" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>НХК-Ден-Деветак-Съно-НХК</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>ДИРОСИ ООД</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>СТАНИСЛАВ ДИМИТРОВ ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>А1535ВВ</t>
+        </is>
+      </c>
+      <c r="J268" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="K268" s="2" t="n">
+        <v>13000</v>
+      </c>
+      <c r="L268" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="M268" s="3" t="n">
+        <v>10.46153846153846</v>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P268" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U268" s="4" t="n">
+        <v>46240.75967954861</v>
+      </c>
+      <c r="V268" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W268" s="4" t="n">
+        <v>46240.76422670139</v>
+      </c>
+      <c r="X268" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y268" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z268" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="19.2" customHeight="1">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>20260806-0012</t>
+        </is>
+      </c>
+      <c r="B269" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>НХК-Чайка-НХК</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>РОСБУЛ ТРАНС</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Милен Иванов Атанасов</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>А1535ВВ</t>
+        </is>
+      </c>
+      <c r="J269" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="K269" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L269" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="M269" s="3" t="n">
+        <v>56.66666666666666</v>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U269" s="4" t="n">
+        <v>46240.76065498843</v>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W269" s="4" t="n">
+        <v>46240.7617344213</v>
+      </c>
+      <c r="X269" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y269" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z269" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="19.2" customHeight="1">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>20260806-0013</t>
+        </is>
+      </c>
+      <c r="B270" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Тервел-Гешаново-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>B7902TM</t>
+        </is>
+      </c>
+      <c r="J270" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="K270" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L270" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M270" s="3" t="n">
+        <v>166.6666666666667</v>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P270" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U270" s="4" t="n">
+        <v>46240.76179599537</v>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W270" s="4" t="n">
+        <v>46240.76312576389</v>
+      </c>
+      <c r="X270" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y270" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z270" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="19.2" customHeight="1">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>20260806-0014</t>
+        </is>
+      </c>
+      <c r="B271" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J271" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="K271" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L271" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="M271" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P271" s="2" t="n">
+        <v>14000</v>
+      </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U271" s="4" t="n">
+        <v>46240.76433942129</v>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W271" s="4" t="n">
+        <v>46244.64200315972</v>
+      </c>
+      <c r="X271" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y271" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z271" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="19.2" customHeight="1">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>20260810-0001</t>
+        </is>
+      </c>
+      <c r="B272" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Русе-Бяла-Енево-Тервел-Русе</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="J272" s="2" t="n">
+        <v>420</v>
+      </c>
+      <c r="K272" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L272" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="M272" s="3" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P272" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U272" s="4" t="n">
+        <v>46244.64204703704</v>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W272" s="4" t="n">
+        <v>46244.64334456019</v>
+      </c>
+      <c r="X272" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y272" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z272" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="19.2" customHeight="1">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>20260810-0002</t>
+        </is>
+      </c>
+      <c r="B273" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Варна-нхк-Каварна-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J273" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="K273" s="2" t="n">
+        <v>31000</v>
+      </c>
+      <c r="L273" s="2" t="n">
+        <v>540</v>
+      </c>
+      <c r="M273" s="3" t="n">
+        <v>17.41935483870968</v>
+      </c>
+      <c r="N273" s="2" t="n">
+        <v>18500</v>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P273" s="2" t="n">
+        <v>18500</v>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U273" s="4" t="n">
+        <v>46244.64341319445</v>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W273" s="4" t="n">
+        <v>46244.64645126157</v>
+      </c>
+      <c r="X273" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="19.2" customHeight="1">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>20260810-0003</t>
+        </is>
+      </c>
+      <c r="B274" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>НХК-Чайка хотел- НХК</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>РОСБУЛ ТРАНС</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>МИЛЕН СТЕФАНОВ АНДРЕЕВ</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>А2106НР</t>
+        </is>
+      </c>
+      <c r="J274" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="K274" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L274" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="M274" s="3" t="n">
+        <v>56.66666666666666</v>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U274" s="4" t="n">
+        <v>46244.64656255787</v>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W274" s="4" t="n">
+        <v>46244.64750273148</v>
+      </c>
+      <c r="X274" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y274" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z274" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="19.2" customHeight="1">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>20260810-0004</t>
+        </is>
+      </c>
+      <c r="B275" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J275" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="K275" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L275" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="M275" s="3" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P275" s="2" t="n">
+        <v>15600</v>
+      </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U275" s="4" t="n">
+        <v>46244.64761892361</v>
+      </c>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W275" s="4" t="n">
+        <v>46247.32354059027</v>
+      </c>
+      <c r="X275" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y275" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z275" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="19.2" customHeight="1">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>20260810-0005</t>
+        </is>
+      </c>
+      <c r="B276" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Варна-Хидро-Варна</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J276" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="K276" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L276" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="M276" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P276" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U276" s="4" t="n">
+        <v>46244.64932045139</v>
+      </c>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W276" s="4" t="n">
+        <v>46247.32307840278</v>
+      </c>
+      <c r="X276" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y276" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z276" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="19.2" customHeight="1">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>20260813-0001</t>
+        </is>
+      </c>
+      <c r="B277" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Русе-Мечка-Русе</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>ЕЛ-ПЛАМ ТРАНС ЕООД</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>ЕЛКО ИВАНОВ ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>СВ5456СМ</t>
+        </is>
+      </c>
+      <c r="J277" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="K277" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L277" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="M277" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P277" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U277" s="4" t="n">
+        <v>46247.32360550926</v>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W277" s="4" t="n">
+        <v>46247.32470684028</v>
+      </c>
+      <c r="X277" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y277" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z277" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="19.2" customHeight="1">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>20260813-0002</t>
+        </is>
+      </c>
+      <c r="B278" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>НХк-Община Поморие-НХК</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>ДЪЛВАН ЕООД</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>ИВАН ГЕОРГИЕВ ТУРМАНОВ</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>А7660КР</t>
+        </is>
+      </c>
+      <c r="J278" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="K278" s="2" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L278" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="M278" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P278" s="2" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U278" s="4" t="n">
+        <v>46247.3248256713</v>
+      </c>
+      <c r="V278" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W278" s="4" t="n">
+        <v>46247.32540394676</v>
+      </c>
+      <c r="X278" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y278" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z278" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="19.2" customHeight="1">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>20260813-0003</t>
+        </is>
+      </c>
+      <c r="B279" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Каварна-Шабла-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J279" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="K279" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L279" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="M279" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="N279" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P279" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U279" s="4" t="n">
+        <v>46247.32544461806</v>
+      </c>
+      <c r="V279" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W279" s="4" t="n">
+        <v>46247.33645689815</v>
+      </c>
+      <c r="X279" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y279" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z279" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="19.2" customHeight="1">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>20260813-0004</t>
+        </is>
+      </c>
+      <c r="B280" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Варна-Малина-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>B7902TM</t>
+        </is>
+      </c>
+      <c r="J280" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="K280" s="2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L280" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="M280" s="3" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P280" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U280" s="4" t="n">
+        <v>46247.3364921875</v>
+      </c>
+      <c r="V280" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W280" s="4" t="n">
+        <v>46247.42416609954</v>
+      </c>
+      <c r="X280" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y280" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z280" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="19.2" customHeight="1">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>20260813-0005</t>
+        </is>
+      </c>
+      <c r="B281" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Варна-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>B7902TM</t>
+        </is>
+      </c>
+      <c r="J281" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K281" s="2" t="n">
+        <v>16000</v>
+      </c>
+      <c r="L281" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="M281" s="3" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U281" s="4" t="n">
+        <v>46247.42525802083</v>
+      </c>
+      <c r="V281" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W281" s="4" t="n">
+        <v>46247.42672533564</v>
+      </c>
+      <c r="X281" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y281" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z281" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="19.2" customHeight="1">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>20260813-0006</t>
+        </is>
+      </c>
+      <c r="B282" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Русе-Тервел-Нова Камена-Карапелит-Русе</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="J282" s="2" t="n">
+        <v>390</v>
+      </c>
+      <c r="K282" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L282" s="2" t="n">
+        <v>468</v>
+      </c>
+      <c r="M282" s="3" t="n">
+        <v>14.625</v>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P282" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U282" s="4" t="n">
+        <v>46247.42680295139</v>
+      </c>
+      <c r="V282" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W282" s="4" t="n">
+        <v>46247.42994275463</v>
+      </c>
+      <c r="X282" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y282" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z282" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="19.2" customHeight="1">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>20260813-0007</t>
+        </is>
+      </c>
+      <c r="B283" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Дългопол-Брестак-Киселово-Варна</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J283" s="2" t="n">
+        <v>230</v>
+      </c>
+      <c r="K283" s="2" t="n">
+        <v>35000</v>
+      </c>
+      <c r="L283" s="2" t="n">
+        <v>276</v>
+      </c>
+      <c r="M283" s="3" t="n">
+        <v>7.885714285714286</v>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P283" s="2" t="n">
+        <v>35000</v>
+      </c>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U283" s="4" t="n">
+        <v>46247.42998789352</v>
+      </c>
+      <c r="V283" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W283" s="4" t="n">
+        <v>46247.43157589121</v>
+      </c>
+      <c r="X283" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y283" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z283" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="19.2" customHeight="1">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>20260819-0001</t>
+        </is>
+      </c>
+      <c r="B284" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Варна-Бомби-КРЗ-Братя-Салс-Киров-Варна</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J284" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="K284" s="2" t="n">
+        <v>36400</v>
+      </c>
+      <c r="L284" s="2" t="n">
+        <v>384</v>
+      </c>
+      <c r="M284" s="3" t="n">
+        <v>10.54945054945055</v>
+      </c>
+      <c r="N284" s="2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P284" s="2" t="n">
+        <v>26400</v>
+      </c>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U284" s="4" t="n">
+        <v>46253.44973041667</v>
+      </c>
+      <c r="V284" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W284" s="4" t="n">
+        <v>46253.45206186343</v>
+      </c>
+      <c r="X284" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y284" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z284" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="19.2" customHeight="1">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>20260819-0002</t>
+        </is>
+      </c>
+      <c r="B285" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Р2530ЕЕ</t>
+        </is>
+      </c>
+      <c r="J285" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="K285" s="2" t="n">
+        <v>28300</v>
+      </c>
+      <c r="L285" s="2" t="n">
+        <v>336</v>
+      </c>
+      <c r="M285" s="3" t="n">
+        <v>11.87279151943463</v>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U285" s="4" t="n">
+        <v>46253.45210194444</v>
+      </c>
+      <c r="V285" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W285" s="4" t="n">
+        <v>46253.45332358796</v>
+      </c>
+      <c r="X285" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y285" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z285" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="19.2" customHeight="1">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>20260819-0003</t>
+        </is>
+      </c>
+      <c r="B286" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Варна-Ген.Тошево-Сенокос-Варна</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>B7902TM</t>
+        </is>
+      </c>
+      <c r="J286" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="K286" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L286" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="M286" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P286" s="2" t="n">
+        <v>14000</v>
+      </c>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U286" s="4" t="n">
+        <v>46253.45335928241</v>
+      </c>
+      <c r="V286" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W286" s="4" t="n">
+        <v>46253.45457443287</v>
+      </c>
+      <c r="X286" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y286" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z286" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="19.2" customHeight="1">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>20260819-0004</t>
+        </is>
+      </c>
+      <c r="B287" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Русе-Снежина-Русе</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>АЛМА ТРАНС ЕООД</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Теодор Александров Георгиев</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>ОВ7977ВА</t>
+        </is>
+      </c>
+      <c r="J287" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="K287" s="2" t="n">
+        <v>18700</v>
+      </c>
+      <c r="L287" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="M287" s="3" t="n">
+        <v>15.02673796791444</v>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P287" s="2" t="n">
+        <v>18700</v>
+      </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U287" s="4" t="n">
+        <v>46253.45460394676</v>
+      </c>
+      <c r="V287" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W287" s="4" t="n">
+        <v>46253.47334265046</v>
+      </c>
+      <c r="X287" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y287" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z287" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="19.2" customHeight="1">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>20260819-0005</t>
+        </is>
+      </c>
+      <c r="B288" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Русе-Тервел-Кладенци-Жегларци-Русе</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>АЛМА ТРАНС ЕООД</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Теодор Александров Георгиев</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>ОВ7977ВА</t>
+        </is>
+      </c>
+      <c r="J288" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="K288" s="2" t="n">
+        <v>17500</v>
+      </c>
+      <c r="L288" s="2" t="n">
+        <v>331</v>
+      </c>
+      <c r="M288" s="3" t="n">
+        <v>18.91428571428571</v>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P288" s="2" t="n">
+        <v>17500</v>
+      </c>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U288" s="4" t="n">
+        <v>46253.47354578703</v>
+      </c>
+      <c r="V288" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W288" s="4" t="n">
+        <v>46253.47483068287</v>
+      </c>
+      <c r="X288" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y288" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z288" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="19.2" customHeight="1">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>20260819-0006</t>
+        </is>
+      </c>
+      <c r="B289" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>НХК-Каблешково-Слънчев бряг-НХК</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>РОСБУЛ ТРАНС</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Милен Иванов Атанасов</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>А2106НР</t>
+        </is>
+      </c>
+      <c r="J289" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K289" s="2" t="n">
+        <v>7800</v>
+      </c>
+      <c r="L289" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="M289" s="3" t="n">
+        <v>10.8974358974359</v>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P289" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U289" s="4" t="n">
+        <v>46253.47493780093</v>
+      </c>
+      <c r="V289" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W289" s="4" t="n">
+        <v>46253.47946357639</v>
+      </c>
+      <c r="X289" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y289" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z289" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="19.2" customHeight="1">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>20260819-0007</t>
+        </is>
+      </c>
+      <c r="B290" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Енево-Варна</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="J290" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="K290" s="2" t="n">
+        <v>26200</v>
+      </c>
+      <c r="L290" s="2" t="n">
+        <v>252</v>
+      </c>
+      <c r="M290" s="3" t="n">
+        <v>9.618320610687023</v>
+      </c>
+      <c r="N290" s="2" t="n">
+        <v>11200</v>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P290" s="2" t="n">
+        <v>25200</v>
+      </c>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U290" s="4" t="n">
+        <v>46253.47952993056</v>
+      </c>
+      <c r="V290" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W290" s="4" t="n">
+        <v>46253.48405149305</v>
+      </c>
+      <c r="X290" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y290" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z290" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="19.2" customHeight="1">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>20260819-0008</t>
+        </is>
+      </c>
+      <c r="B291" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Пчелник-Девня-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>"СИ-ТРАНС БЪЛГАРИЯ"  ЕООД</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Живко Демиров Вълчев</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>В9261РА</t>
+        </is>
+      </c>
+      <c r="J291" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="K291" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L291" s="2" t="n">
+        <v>420</v>
+      </c>
+      <c r="M291" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T291" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U291" s="4" t="n">
+        <v>46253.48409303241</v>
+      </c>
+      <c r="V291" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W291" s="4" t="n">
+        <v>46253.4856337963</v>
+      </c>
+      <c r="X291" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y291" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z291" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="19.2" customHeight="1">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>20260819-0009</t>
+        </is>
+      </c>
+      <c r="B292" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Русе-Тервел-Риш-Невестино-Деветак-НХК</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="J292" s="2" t="n">
+        <v>440</v>
+      </c>
+      <c r="K292" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L292" s="2" t="n">
+        <v>528</v>
+      </c>
+      <c r="M292" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P292" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T292" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U292" s="4" t="n">
+        <v>46253.4857122338</v>
+      </c>
+      <c r="V292" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W292" s="4" t="n">
+        <v>46258.70121236111</v>
+      </c>
+      <c r="X292" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y292" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z292" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="19.2" customHeight="1">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>20260824-0001</t>
+        </is>
+      </c>
+      <c r="B293" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Варна-Добрич-Красен-Варна</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>B7902TM</t>
+        </is>
+      </c>
+      <c r="J293" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="K293" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L293" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="M293" s="3" t="n">
+        <v>18.33333333333333</v>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P293" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="T293" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U293" s="4" t="n">
+        <v>46258.70141886574</v>
+      </c>
+      <c r="V293" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W293" s="4" t="n">
+        <v>46258.70329149305</v>
+      </c>
+      <c r="X293" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y293" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z293" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="19.2" customHeight="1">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>20260824-0002</t>
+        </is>
+      </c>
+      <c r="B294" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Варна-Каварна-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>B7902TM</t>
+        </is>
+      </c>
+      <c r="J294" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="K294" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L294" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="M294" s="3" t="n">
+        <v>10.55555555555556</v>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P294" s="2" t="n">
+        <v>13000</v>
+      </c>
+      <c r="T294" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U294" s="4" t="n">
+        <v>46258.70332947917</v>
+      </c>
+      <c r="V294" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W294" s="4" t="n">
+        <v>46258.70728408565</v>
+      </c>
+      <c r="X294" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y294" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z294" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="19.2" customHeight="1">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>20260824-0003</t>
+        </is>
+      </c>
+      <c r="B295" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>НХК-Долни Чифлик - Каварна - Метличина - Карапелит - Житница - Тервел - Русе</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="J295" s="2" t="n">
+        <v>590</v>
+      </c>
+      <c r="K295" s="2" t="n">
+        <v>32300</v>
+      </c>
+      <c r="L295" s="2" t="n">
+        <v>708</v>
+      </c>
+      <c r="M295" s="3" t="n">
+        <v>21.91950464396285</v>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P295" s="2" t="n">
+        <v>32300</v>
+      </c>
+      <c r="T295" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U295" s="4" t="n">
+        <v>46258.70732233796</v>
+      </c>
+      <c r="V295" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W295" s="4" t="n">
+        <v>46258.71006979167</v>
+      </c>
+      <c r="X295" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y295" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z295" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="19.2" customHeight="1">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>20260824-0004</t>
+        </is>
+      </c>
+      <c r="B296" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Пчелник-Каварна-Малина-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>"СИ-ТРАНС БЪЛГАРИЯ"  ЕООД</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>Живко Демиров Вълчев</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>В9296ТМ</t>
+        </is>
+      </c>
+      <c r="J296" s="2" t="n">
+        <v>516</v>
+      </c>
+      <c r="K296" s="2" t="n">
+        <v>31000</v>
+      </c>
+      <c r="L296" s="2" t="n">
+        <v>550</v>
+      </c>
+      <c r="M296" s="3" t="n">
+        <v>17.74193548387097</v>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P296" s="2" t="n">
+        <v>22200</v>
+      </c>
+      <c r="T296" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U296" s="4" t="n">
+        <v>46258.71017533565</v>
+      </c>
+      <c r="V296" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W296" s="4" t="n">
+        <v>46259.43945784722</v>
+      </c>
+      <c r="X296" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y296" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z296" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="19.2" customHeight="1">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>20260824-0005</t>
+        </is>
+      </c>
+      <c r="B297" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Русе-Тервел-Брестак-Ген. Колево - Добрич -Аспарухово</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J297" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="K297" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L297" s="2" t="n">
+        <v>480</v>
+      </c>
+      <c r="M297" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P297" s="2" t="n">
+        <v>28000</v>
+      </c>
+      <c r="T297" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U297" s="4" t="n">
+        <v>46258.71245950231</v>
+      </c>
+      <c r="V297" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W297" s="4" t="n">
+        <v>46258.71662456018</v>
+      </c>
+      <c r="X297" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y297" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z297" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="19.2" customHeight="1">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>20260825-0001</t>
+        </is>
+      </c>
+      <c r="B298" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Салс-Салс</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>"СИ-ТРАНС БЪЛГАРИЯ"  ЕООД</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>Живко Демиров Вълчев</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>В9296ТМ</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>В6351ЕН</t>
+        </is>
+      </c>
+      <c r="K298" s="2" t="n">
+        <v>8500</v>
+      </c>
+      <c r="L298" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="M298" s="3" t="n">
+        <v>14.11764705882353</v>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P298" s="2" t="n">
+        <v>8500</v>
+      </c>
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U298" s="4" t="n">
+        <v>46259.60008709491</v>
+      </c>
+      <c r="V298" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W298" s="4" t="n">
+        <v>46262.65285101852</v>
+      </c>
+      <c r="X298" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y298" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z298" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="19.2" customHeight="1">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>20260825-0002</t>
+        </is>
+      </c>
+      <c r="B299" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Русе-Бяла-Орешец</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>ЕЛ-ПЛАМ ТРАНС ЕООД</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>ТОДОР  ДИМИТРОВ ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>В9261РА</t>
+        </is>
+      </c>
+      <c r="J299" s="2" t="n">
+        <v>335</v>
+      </c>
+      <c r="K299" s="2" t="n">
+        <v>18700</v>
+      </c>
+      <c r="L299" s="2" t="n">
+        <v>570</v>
+      </c>
+      <c r="M299" s="3" t="n">
+        <v>30.48128342245989</v>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P299" s="2" t="n">
+        <v>18700</v>
+      </c>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U299" s="4" t="n">
+        <v>46259.60184413195</v>
+      </c>
+      <c r="V299" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W299" s="4" t="n">
+        <v>46259.60305853009</v>
+      </c>
+      <c r="X299" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y299" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z299" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="19.2" customHeight="1">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>20260825-0003</t>
+        </is>
+      </c>
+      <c r="B300" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>НХК-Калина Гадън-НХК</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>ДИРОСИ ООД</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>СТАНИСЛАВ ДИМИТРОВ ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>А1535ВВ</t>
+        </is>
+      </c>
+      <c r="K300" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L300" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="M300" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T300" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U300" s="4" t="n">
+        <v>46259.60308570602</v>
+      </c>
+      <c r="V300" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W300" s="4" t="n">
+        <v>46259.60364623843</v>
+      </c>
+      <c r="X300" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y300" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z300" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="19.2" customHeight="1">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>20260825-0004</t>
+        </is>
+      </c>
+      <c r="B301" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Бяла-Добрич-Варна-НХК</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="J301" s="2" t="n">
+        <v>520</v>
+      </c>
+      <c r="K301" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L301" s="2" t="n">
+        <v>624</v>
+      </c>
+      <c r="M301" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P301" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="T301" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U301" s="4" t="n">
+        <v>46259.60367255787</v>
+      </c>
+      <c r="V301" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W301" s="4" t="n">
+        <v>46259.60668869213</v>
+      </c>
+      <c r="X301" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y301" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z301" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="19.2" customHeight="1">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>20260825-0005</t>
+        </is>
+      </c>
+      <c r="B302" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>СЗ-Бяла-СЗ-Крепост-Димитровград-СЗ</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>ЗАРА Е</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>СТЕФАН ГОСПОДИНОВ СТАЛЕВ</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>СТ4211РА</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>СТ3099ЕН</t>
+        </is>
+      </c>
+      <c r="J302" s="2" t="n">
+        <v>451</v>
+      </c>
+      <c r="K302" s="2" t="n">
+        <v>31000</v>
+      </c>
+      <c r="L302" s="2" t="n">
+        <v>587</v>
+      </c>
+      <c r="M302" s="3" t="n">
+        <v>18.93548387096774</v>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P302" s="2" t="n">
+        <v>27000</v>
+      </c>
+      <c r="T302" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U302" s="4" t="n">
+        <v>46259.6091428588</v>
+      </c>
+      <c r="V302" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W302" s="4" t="n">
+        <v>46262.62206979167</v>
+      </c>
+      <c r="X302" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y302" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z302" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="19.2" customHeight="1">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>20260828-0001</t>
+        </is>
+      </c>
+      <c r="B303" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Русе-Повеляново-Калиманци - Каварна-Русе</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="J303" s="2" t="n">
+        <v>520</v>
+      </c>
+      <c r="K303" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L303" s="2" t="n">
+        <v>624</v>
+      </c>
+      <c r="M303" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P303" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T303" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U303" s="4" t="n">
+        <v>46262.62210945602</v>
+      </c>
+      <c r="V303" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W303" s="4" t="n">
+        <v>46262.62692824074</v>
+      </c>
+      <c r="X303" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y303" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z303" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="19.2" customHeight="1">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>20260828-0002</t>
+        </is>
+      </c>
+      <c r="B304" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Бяла-Русе-Северняк-Добрич-Варна-Русе</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>СДР Трайл ЕООД</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>РОМАН ЙОРДАНОВ ЗДРАВКОВ</t>
+        </is>
+      </c>
+      <c r="J304" s="2" t="n">
+        <v>550</v>
+      </c>
+      <c r="K304" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L304" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="M304" s="3" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P304" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T304" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U304" s="4" t="n">
+        <v>46262.62697130787</v>
+      </c>
+      <c r="V304" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W304" s="4" t="n">
+        <v>46262.62812802083</v>
+      </c>
+      <c r="X304" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y304" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z304" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="19.2" customHeight="1">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>20260828-0003</t>
+        </is>
+      </c>
+      <c r="B305" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Бяла-Варна-Добрич-Русе</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="J305" s="2" t="n">
+        <v>470</v>
+      </c>
+      <c r="K305" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L305" s="2" t="n">
+        <v>564</v>
+      </c>
+      <c r="M305" s="3" t="n">
+        <v>17.625</v>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P305" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="T305" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U305" s="4" t="n">
+        <v>46262.62816707176</v>
+      </c>
+      <c r="V305" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W305" s="4" t="n">
+        <v>46262.6311090625</v>
+      </c>
+      <c r="X305" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y305" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z305" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="19.2" customHeight="1">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>20260828-0004</t>
+        </is>
+      </c>
+      <c r="B306" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Бяла-Варна-Добрич-Тервел-Русе</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>ВЕНЦИСЛАВ КРУМОВ</t>
+        </is>
+      </c>
+      <c r="J306" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="K306" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L306" s="2" t="n">
+        <v>550</v>
+      </c>
+      <c r="M306" s="3" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P306" s="2" t="n">
+        <v>7000</v>
+      </c>
+      <c r="T306" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U306" s="4" t="n">
+        <v>46262.63115662037</v>
+      </c>
+      <c r="V306" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W306" s="4" t="n">
+        <v>46262.63226666667</v>
+      </c>
+      <c r="X306" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y306" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z306" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="19.2" customHeight="1">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>20260828-0005</t>
+        </is>
+      </c>
+      <c r="B307" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Каварна-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="J307" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="K307" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L307" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="M307" s="3" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="N307" s="2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P307" s="2" t="n">
+        <v>16000</v>
+      </c>
+      <c r="T307" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U307" s="4" t="n">
+        <v>46262.63231280092</v>
+      </c>
+      <c r="V307" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W307" s="4" t="n">
+        <v>46262.63573277778</v>
+      </c>
+      <c r="X307" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y307" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z307" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="19.2" customHeight="1">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>20260828-0006</t>
+        </is>
+      </c>
+      <c r="B308" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Русе-Тервел-Нова Камена - Гешаново-Русе</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="J308" s="2" t="n">
+        <v>440</v>
+      </c>
+      <c r="K308" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L308" s="2" t="n">
+        <v>528</v>
+      </c>
+      <c r="M308" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P308" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T308" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U308" s="4" t="n">
+        <v>46262.63578925926</v>
+      </c>
+      <c r="V308" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W308" s="4" t="n">
+        <v>46262.63877578704</v>
+      </c>
+      <c r="X308" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y308" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z308" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="19.2" customHeight="1">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>20260831-0001</t>
+        </is>
+      </c>
+      <c r="B309" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>НХК-Поморие</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>ДЪЛВАН ЕООД</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>ИВАН ГЕОРГИЕВ ТУРМАНОВ</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>А7660КР</t>
+        </is>
+      </c>
+      <c r="K309" s="2" t="n">
+        <v>8000</v>
+      </c>
+      <c r="M309" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P309" s="2" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T309" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U309" s="4" t="n">
+        <v>46265.65786912037</v>
+      </c>
+      <c r="V309" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W309" s="4" t="n">
+        <v>46265.65914315972</v>
+      </c>
+      <c r="X309" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y309" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z309" t="inlineStr">
+        <is>
+          <t>31</t>
         </is>
       </c>
     </row>

--- a/transport/transport_data.xlsx
+++ b/transport/transport_data.xlsx
@@ -28540,6 +28540,5618 @@
         </is>
       </c>
     </row>
+    <row r="310" ht="19.2" customHeight="1">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>20260908-0001</t>
+        </is>
+      </c>
+      <c r="B310" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Русе- Кацелово-Копривец-Островче-Ушинци</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>ЕЛ-ПЛАМ ТРАНС ЕООД</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>ЕЛКО ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="J310" s="2" t="n">
+        <v>237</v>
+      </c>
+      <c r="K310" s="2" t="n">
+        <v>15800</v>
+      </c>
+      <c r="L310" s="2" t="n">
+        <v>403</v>
+      </c>
+      <c r="M310" s="3" t="n">
+        <v>25.50632911392405</v>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P310" s="2" t="n">
+        <v>3800</v>
+      </c>
+      <c r="T310" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U310" s="4" t="n">
+        <v>46273.73616655092</v>
+      </c>
+      <c r="V310" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W310" s="4" t="n">
+        <v>46280.51179708333</v>
+      </c>
+      <c r="X310" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y310" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z310" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="19.2" customHeight="1">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>20260908-0002</t>
+        </is>
+      </c>
+      <c r="B311" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Русе-Войново-Тервел</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>ЕЛ-ПЛАМ ТРАНС ЕООД</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>ЕЛКО ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="J311" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="K311" s="2" t="n">
+        <v>18700</v>
+      </c>
+      <c r="L311" s="2" t="n">
+        <v>289</v>
+      </c>
+      <c r="M311" s="3" t="n">
+        <v>15.45454545454546</v>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P311" s="2" t="n">
+        <v>18700</v>
+      </c>
+      <c r="T311" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U311" s="4" t="n">
+        <v>46273.74273721065</v>
+      </c>
+      <c r="V311" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W311" s="4" t="n">
+        <v>46273.74463137732</v>
+      </c>
+      <c r="X311" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y311" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z311" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="19.2" customHeight="1">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>20260908-0003</t>
+        </is>
+      </c>
+      <c r="B312" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Варна-Лукойл база Аспарухово-Любен-Сенокос-Варна</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>B7902TM</t>
+        </is>
+      </c>
+      <c r="J312" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="K312" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L312" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="M312" s="3" t="n">
+        <v>16.66666666666667</v>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P312" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="T312" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U312" s="4" t="n">
+        <v>46273.74467299769</v>
+      </c>
+      <c r="V312" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W312" s="4" t="n">
+        <v>46273.74582336806</v>
+      </c>
+      <c r="X312" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y312" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z312" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="19.2" customHeight="1">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>20260908-0004</t>
+        </is>
+      </c>
+      <c r="B313" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Енево-Есеница-Девня-Варна</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J313" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="K313" s="2" t="n">
+        <v>32300</v>
+      </c>
+      <c r="L313" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="M313" s="3" t="n">
+        <v>9.287925696594426</v>
+      </c>
+      <c r="N313" s="2" t="n">
+        <v>14000</v>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P313" s="2" t="n">
+        <v>32300</v>
+      </c>
+      <c r="T313" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U313" s="4" t="n">
+        <v>46273.745934375</v>
+      </c>
+      <c r="V313" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W313" s="4" t="n">
+        <v>46273.74872</v>
+      </c>
+      <c r="X313" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y313" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z313" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="19.2" customHeight="1">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>20260908-0005</t>
+        </is>
+      </c>
+      <c r="B314" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Дългопол-Блъсково-Брестак-Нова Камена-Тервел-Черна-Добрич-Брестак-Варна</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J314" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="K314" s="2" t="n">
+        <v>35500</v>
+      </c>
+      <c r="L314" s="2" t="n">
+        <v>480</v>
+      </c>
+      <c r="M314" s="3" t="n">
+        <v>13.52112676056338</v>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P314" s="2" t="n">
+        <v>28500</v>
+      </c>
+      <c r="T314" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U314" s="4" t="n">
+        <v>46273.74878560185</v>
+      </c>
+      <c r="V314" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W314" s="4" t="n">
+        <v>46273.75278450231</v>
+      </c>
+      <c r="X314" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y314" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z314" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="19.2" customHeight="1">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>20260908-0006</t>
+        </is>
+      </c>
+      <c r="B315" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>НХК-Невестино-Риш-Нова Бяла река-НХК</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>ДИРОСИ ООД</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>СТАНИСЛАВ ДИМИТРОВ ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>А1535ВВ</t>
+        </is>
+      </c>
+      <c r="J315" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="K315" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L315" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="M315" s="3" t="n">
+        <v>11.55555555555556</v>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P315" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="T315" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U315" s="4" t="n">
+        <v>46273.75293810185</v>
+      </c>
+      <c r="V315" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W315" s="4" t="n">
+        <v>46273.75581945602</v>
+      </c>
+      <c r="X315" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y315" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z315" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="19.2" customHeight="1">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>20260908-0007</t>
+        </is>
+      </c>
+      <c r="B316" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Каварна-добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J316" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="K316" s="2" t="n">
+        <v>33000</v>
+      </c>
+      <c r="L316" s="2" t="n">
+        <v>540</v>
+      </c>
+      <c r="M316" s="3" t="n">
+        <v>16.36363636363636</v>
+      </c>
+      <c r="N316" s="2" t="n">
+        <v>21000</v>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P316" s="2" t="n">
+        <v>21000</v>
+      </c>
+      <c r="T316" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U316" s="4" t="n">
+        <v>46273.75603104167</v>
+      </c>
+      <c r="V316" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W316" s="4" t="n">
+        <v>46273.75996368055</v>
+      </c>
+      <c r="X316" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y316" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z316" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="19.2" customHeight="1">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>20260908-0008</t>
+        </is>
+      </c>
+      <c r="B317" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Аспарухово-Кипра-Вълчи дол-Ботево-Варна-Повеляново-Вълчи дол-Аспарухово</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="J317" s="2" t="n">
+        <v>305</v>
+      </c>
+      <c r="K317" s="2" t="n">
+        <v>32800</v>
+      </c>
+      <c r="L317" s="2" t="n">
+        <v>366</v>
+      </c>
+      <c r="M317" s="3" t="n">
+        <v>11.15853658536585</v>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P317" s="2" t="n">
+        <v>32800</v>
+      </c>
+      <c r="T317" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U317" s="4" t="n">
+        <v>46273.76007943287</v>
+      </c>
+      <c r="V317" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W317" s="4" t="n">
+        <v>46273.76287579861</v>
+      </c>
+      <c r="X317" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y317" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z317" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="19.2" customHeight="1">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>20260908-0009</t>
+        </is>
+      </c>
+      <c r="B318" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>НХК-хотели</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>ДИРОСИ ООД</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>СТАНИСЛАВ ДИМИТРОВ ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>А1535ВВ</t>
+        </is>
+      </c>
+      <c r="J318" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K318" s="2" t="n">
+        <v>3500</v>
+      </c>
+      <c r="L318" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="M318" s="3" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U318" s="4" t="n">
+        <v>46273.76294291667</v>
+      </c>
+      <c r="V318" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W318" s="4" t="n">
+        <v>46273.76376372685</v>
+      </c>
+      <c r="X318" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y318" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z318" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="19.2" customHeight="1">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>20260908-0010</t>
+        </is>
+      </c>
+      <c r="B319" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Хидро</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J319" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="K319" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L319" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="M319" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P319" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T319" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U319" s="4" t="n">
+        <v>46273.7638015625</v>
+      </c>
+      <c r="V319" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W319" s="4" t="n">
+        <v>46273.76463025463</v>
+      </c>
+      <c r="X319" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y319" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z319" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="19.2" customHeight="1">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>20260908-0011</t>
+        </is>
+      </c>
+      <c r="B320" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Блъсково-Добрич-Ген. Тошево-Малина-Варна</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J320" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="K320" s="2" t="n">
+        <v>35500</v>
+      </c>
+      <c r="L320" s="2" t="n">
+        <v>384</v>
+      </c>
+      <c r="M320" s="3" t="n">
+        <v>10.8169014084507</v>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P320" s="2" t="n">
+        <v>22000</v>
+      </c>
+      <c r="T320" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U320" s="4" t="n">
+        <v>46273.76465923611</v>
+      </c>
+      <c r="V320" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W320" s="4" t="n">
+        <v>46273.76665253472</v>
+      </c>
+      <c r="X320" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y320" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z320" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="19.2" customHeight="1">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>20260908-0012</t>
+        </is>
+      </c>
+      <c r="B321" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Аспарухово-Добрич-Тервел-Русе</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="J321" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="K321" s="2" t="n">
+        <v>32500</v>
+      </c>
+      <c r="L321" s="2" t="n">
+        <v>396</v>
+      </c>
+      <c r="M321" s="3" t="n">
+        <v>12.18461538461538</v>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P321" s="2" t="n">
+        <v>14000</v>
+      </c>
+      <c r="T321" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U321" s="4" t="n">
+        <v>46273.76680313658</v>
+      </c>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W321" s="4" t="n">
+        <v>46273.76864482639</v>
+      </c>
+      <c r="X321" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y321" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z321" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="19.2" customHeight="1">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>20260908-0013</t>
+        </is>
+      </c>
+      <c r="B322" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Русе-Ясеновец-Подайва</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>ЕЛ-ПЛАМ ТРАНС ЕООД</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>ЕЛКО ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="J322" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="K322" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L322" s="2" t="n">
+        <v>203</v>
+      </c>
+      <c r="M322" s="3" t="n">
+        <v>11.27777777777778</v>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P322" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="T322" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U322" s="4" t="n">
+        <v>46273.76870034722</v>
+      </c>
+      <c r="V322" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W322" s="4" t="n">
+        <v>46273.77029375</v>
+      </c>
+      <c r="X322" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y322" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z322" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="19.2" customHeight="1">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>20260908-0014</t>
+        </is>
+      </c>
+      <c r="B323" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Долни Чифлик-Девня-Каварна-Варна</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J323" s="2" t="n">
+        <v>440</v>
+      </c>
+      <c r="K323" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L323" s="2" t="n">
+        <v>528</v>
+      </c>
+      <c r="M323" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="N323" s="2" t="n">
+        <v>21000</v>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P323" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T323" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U323" s="4" t="n">
+        <v>46273.77033759259</v>
+      </c>
+      <c r="V323" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W323" s="4" t="n">
+        <v>46273.77268138889</v>
+      </c>
+      <c r="X323" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y323" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z323" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="19.2" customHeight="1">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>20260908-0015</t>
+        </is>
+      </c>
+      <c r="B324" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Русе-Близнаци-Доброплодно-Добрич-Паскалево-Аспарухово</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="J324" s="2" t="n">
+        <v>390</v>
+      </c>
+      <c r="K324" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L324" s="2" t="n">
+        <v>468</v>
+      </c>
+      <c r="M324" s="3" t="n">
+        <v>14.625</v>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P324" s="2" t="n">
+        <v>11300</v>
+      </c>
+      <c r="T324" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U324" s="4" t="n">
+        <v>46273.77272641204</v>
+      </c>
+      <c r="V324" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W324" s="4" t="n">
+        <v>46273.77507295139</v>
+      </c>
+      <c r="X324" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y324" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z324" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="19.2" customHeight="1">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>20260908-0016</t>
+        </is>
+      </c>
+      <c r="B325" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Русе-Климент-Тервелл-Карапелит-Русе</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="J325" s="2" t="n">
+        <v>380</v>
+      </c>
+      <c r="K325" s="2" t="n">
+        <v>32300</v>
+      </c>
+      <c r="L325" s="2" t="n">
+        <v>456</v>
+      </c>
+      <c r="M325" s="3" t="n">
+        <v>14.11764705882353</v>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P325" s="2" t="n">
+        <v>32300</v>
+      </c>
+      <c r="T325" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U325" s="4" t="n">
+        <v>46273.77512193287</v>
+      </c>
+      <c r="V325" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W325" s="4" t="n">
+        <v>46273.77716534722</v>
+      </c>
+      <c r="X325" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y325" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z325" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="19.2" customHeight="1">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>20260908-0017</t>
+        </is>
+      </c>
+      <c r="B326" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Провадия-Енево-Варна</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J326" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="K326" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L326" s="2" t="n">
+        <v>252</v>
+      </c>
+      <c r="M326" s="3" t="n">
+        <v>7.875</v>
+      </c>
+      <c r="N326" s="2" t="n">
+        <v>10800</v>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P326" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T326" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U326" s="4" t="n">
+        <v>46273.77728480324</v>
+      </c>
+      <c r="V326" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W326" s="4" t="n">
+        <v>46274.68002719907</v>
+      </c>
+      <c r="X326" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y326" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z326" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="19.2" customHeight="1">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>20260908-0018</t>
+        </is>
+      </c>
+      <c r="B327" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Вълчи дол-Ген.Тошево-Варна</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>B7902TM</t>
+        </is>
+      </c>
+      <c r="J327" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="K327" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L327" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="M327" s="3" t="n">
+        <v>16.66666666666667</v>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P327" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="T327" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U327" s="4" t="n">
+        <v>46273.77942770833</v>
+      </c>
+      <c r="V327" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W327" s="4" t="n">
+        <v>46273.780910625</v>
+      </c>
+      <c r="X327" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y327" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z327" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="19.2" customHeight="1">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>20260909-0001</t>
+        </is>
+      </c>
+      <c r="B328" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Аспарухово-Гешаново-Житница-Тервел-Кладенци-Русе</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="J328" s="2" t="n">
+        <v>340</v>
+      </c>
+      <c r="K328" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L328" s="2" t="n">
+        <v>408</v>
+      </c>
+      <c r="M328" s="3" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P328" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T328" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U328" s="4" t="n">
+        <v>46274.67245383102</v>
+      </c>
+      <c r="V328" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W328" s="4" t="n">
+        <v>46274.67492622685</v>
+      </c>
+      <c r="X328" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y328" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z328" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="19.2" customHeight="1">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>20260909-0002</t>
+        </is>
+      </c>
+      <c r="B329" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Каварна-Добрич-Терем-Варна</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J329" s="2" t="n">
+        <v>490</v>
+      </c>
+      <c r="K329" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L329" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="M329" s="3" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="N329" s="2" t="n">
+        <v>16500</v>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P329" s="2" t="n">
+        <v>26500</v>
+      </c>
+      <c r="T329" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U329" s="4" t="n">
+        <v>46274.67496945602</v>
+      </c>
+      <c r="V329" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W329" s="4" t="n">
+        <v>46280.74790799768</v>
+      </c>
+      <c r="X329" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y329" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z329" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="19.2" customHeight="1">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>20260914-0001</t>
+        </is>
+      </c>
+      <c r="B330" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Русе-Блъсково-Русе</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>ЕЛ-ПЛАМ ТРАНС ЕООД</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>ЕЛКО ИВАНОВ ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="J330" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="K330" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L330" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="M330" s="3" t="n">
+        <v>15.61111111111111</v>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P330" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="T330" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U330" s="4" t="n">
+        <v>46279.71925423611</v>
+      </c>
+      <c r="V330" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W330" s="4" t="n">
+        <v>46279.71998798611</v>
+      </c>
+      <c r="X330" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y330" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z330" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" ht="19.2" customHeight="1">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>20260914-0002</t>
+        </is>
+      </c>
+      <c r="B331" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Хидро</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J331" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="K331" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L331" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="M331" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P331" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="T331" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U331" s="4" t="n">
+        <v>46279.72021915509</v>
+      </c>
+      <c r="V331" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W331" s="4" t="n">
+        <v>46279.7209178125</v>
+      </c>
+      <c r="X331" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y331" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z331" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="19.2" customHeight="1">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>20260914-0003</t>
+        </is>
+      </c>
+      <c r="B332" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>АБ + Симо</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>ЗАРА Е</t>
+        </is>
+      </c>
+      <c r="J332" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="K332" s="2" t="n">
+        <v>31000</v>
+      </c>
+      <c r="L332" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="M332" s="3" t="n">
+        <v>4.612903225806451</v>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P332" s="2" t="n">
+        <v>27000</v>
+      </c>
+      <c r="T332" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U332" s="4" t="n">
+        <v>46279.72096678241</v>
+      </c>
+      <c r="V332" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W332" s="4" t="n">
+        <v>46279.72161604166</v>
+      </c>
+      <c r="X332" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y332" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z332" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="19.2" customHeight="1">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>20260914-0004</t>
+        </is>
+      </c>
+      <c r="B333" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J333" s="2" t="n">
+        <v>270</v>
+      </c>
+      <c r="K333" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L333" s="2" t="n">
+        <v>324</v>
+      </c>
+      <c r="M333" s="3" t="n">
+        <v>10.125</v>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T333" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U333" s="4" t="n">
+        <v>46279.72165207176</v>
+      </c>
+      <c r="V333" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W333" s="4" t="n">
+        <v>46279.72348797454</v>
+      </c>
+      <c r="X333" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y333" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z333" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="334" ht="19.2" customHeight="1">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>20260914-0005</t>
+        </is>
+      </c>
+      <c r="B334" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Тервел-Варна</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>B7902TM</t>
+        </is>
+      </c>
+      <c r="J334" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="K334" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L334" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="M334" s="3" t="n">
+        <v>16.66666666666667</v>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P334" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="T334" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U334" s="4" t="n">
+        <v>46279.72353792824</v>
+      </c>
+      <c r="V334" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W334" s="4" t="n">
+        <v>46279.7252112963</v>
+      </c>
+      <c r="X334" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y334" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z334" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="19.2" customHeight="1">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>20260914-0006</t>
+        </is>
+      </c>
+      <c r="B335" s="1" t="n">
+        <v>46277</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>НХК-Пчелник-Повеляново-Крумово-Тервел-Русе</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="J335" s="2" t="n">
+        <v>430</v>
+      </c>
+      <c r="K335" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L335" s="2" t="n">
+        <v>516</v>
+      </c>
+      <c r="M335" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P335" s="2" t="n">
+        <v>23900</v>
+      </c>
+      <c r="T335" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U335" s="4" t="n">
+        <v>46279.72524297453</v>
+      </c>
+      <c r="V335" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W335" s="4" t="n">
+        <v>46279.72751274305</v>
+      </c>
+      <c r="X335" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y335" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z335" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="19.2" customHeight="1">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>20260914-0007</t>
+        </is>
+      </c>
+      <c r="B336" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Неново-Вълчи дол-Ведрина-Малина-Варна</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J336" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="K336" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L336" s="2" t="n">
+        <v>348</v>
+      </c>
+      <c r="M336" s="3" t="n">
+        <v>10.875</v>
+      </c>
+      <c r="N336" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P336" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T336" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U336" s="4" t="n">
+        <v>46279.727575625</v>
+      </c>
+      <c r="V336" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W336" s="4" t="n">
+        <v>46279.72902685186</v>
+      </c>
+      <c r="X336" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y336" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z336" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="19.2" customHeight="1">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>20260914-0008</t>
+        </is>
+      </c>
+      <c r="B337" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Блъсково-Ботево-Варна</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>B7902TM</t>
+        </is>
+      </c>
+      <c r="J337" s="2" t="n">
+        <v>230</v>
+      </c>
+      <c r="K337" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L337" s="2" t="n">
+        <v>230</v>
+      </c>
+      <c r="M337" s="3" t="n">
+        <v>12.77777777777778</v>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P337" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="T337" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U337" s="4" t="n">
+        <v>46279.72908048611</v>
+      </c>
+      <c r="V337" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W337" s="4" t="n">
+        <v>46279.72991554398</v>
+      </c>
+      <c r="X337" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y337" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z337" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="19.2" customHeight="1">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>20260914-0009</t>
+        </is>
+      </c>
+      <c r="B338" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>НХК = Каблешково=Калина</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>ДИРОСИ ООД</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>СТАНИСЛАВ ДИМИТРОВ ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>А5420НХ</t>
+        </is>
+      </c>
+      <c r="J338" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="K338" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L338" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="M338" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P338" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T338" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U338" s="4" t="n">
+        <v>46279.7299588426</v>
+      </c>
+      <c r="V338" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W338" s="4" t="n">
+        <v>46279.73063444444</v>
+      </c>
+      <c r="X338" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y338" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z338" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" ht="19.2" customHeight="1">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>20260915-0001</t>
+        </is>
+      </c>
+      <c r="B339" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Каварна-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J339" s="2" t="n">
+        <v>480</v>
+      </c>
+      <c r="K339" s="2" t="n">
+        <v>33000</v>
+      </c>
+      <c r="L339" s="2" t="n">
+        <v>576</v>
+      </c>
+      <c r="M339" s="3" t="n">
+        <v>17.45454545454546</v>
+      </c>
+      <c r="N339" s="2" t="n">
+        <v>17000</v>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P339" s="2" t="n">
+        <v>19000</v>
+      </c>
+      <c r="T339" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U339" s="4" t="n">
+        <v>46280.74342678241</v>
+      </c>
+      <c r="V339" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W339" s="4" t="n">
+        <v>46280.74848696759</v>
+      </c>
+      <c r="X339" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y339" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z339" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="19.2" customHeight="1">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>20260915-0002</t>
+        </is>
+      </c>
+      <c r="B340" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Провадия-Повеляново -Варна</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>"СИ-ТРАНС БЪЛГАРИЯ"  ЕООД</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>Живко Демиров Вълчев</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>В9261РА</t>
+        </is>
+      </c>
+      <c r="J340" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="K340" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L340" s="2" t="n">
+        <v>242</v>
+      </c>
+      <c r="M340" s="3" t="n">
+        <v>8.066666666666666</v>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P340" s="2" t="n">
+        <v>13000</v>
+      </c>
+      <c r="T340" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U340" s="4" t="n">
+        <v>46280.7485278125</v>
+      </c>
+      <c r="V340" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W340" s="4" t="n">
+        <v>46280.75063892361</v>
+      </c>
+      <c r="X340" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y340" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z340" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="19.2" customHeight="1">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>20260915-0003</t>
+        </is>
+      </c>
+      <c r="B341" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Аспарухово-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>"СИ-ТРАНС БЪЛГАРИЯ"  ЕООД</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>Живко Демиров Вълчев</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>В9261РА</t>
+        </is>
+      </c>
+      <c r="J341" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="K341" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L341" s="2" t="n">
+        <v>396</v>
+      </c>
+      <c r="M341" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T341" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U341" s="4" t="n">
+        <v>46280.75068822916</v>
+      </c>
+      <c r="V341" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W341" s="4" t="n">
+        <v>46280.75167625</v>
+      </c>
+      <c r="X341" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y341" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z341" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="19.2" customHeight="1">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>20260915-0004</t>
+        </is>
+      </c>
+      <c r="B342" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Варна-Енево-Аспарухово-Доброплодно-Жегларци-Карапелит-Киселово-Калиманци-Варна</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J342" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="K342" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L342" s="2" t="n">
+        <v>420</v>
+      </c>
+      <c r="M342" s="3" t="n">
+        <v>13.125</v>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P342" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T342" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U342" s="4" t="n">
+        <v>46280.75182841435</v>
+      </c>
+      <c r="V342" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W342" s="4" t="n">
+        <v>46280.75503144676</v>
+      </c>
+      <c r="X342" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y342" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z342" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" ht="19.2" customHeight="1">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>20260915-0005</t>
+        </is>
+      </c>
+      <c r="B343" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Русе-Островче-Ушинци-Подайва-Тервел-Русе</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="J343" s="2" t="n">
+        <v>370</v>
+      </c>
+      <c r="K343" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L343" s="2" t="n">
+        <v>444</v>
+      </c>
+      <c r="M343" s="3" t="n">
+        <v>13.875</v>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P343" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T343" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U343" s="4" t="n">
+        <v>46280.75511171296</v>
+      </c>
+      <c r="V343" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W343" s="4" t="n">
+        <v>46280.75683678241</v>
+      </c>
+      <c r="X343" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y343" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z343" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="19.2" customHeight="1">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>20260923-0001</t>
+        </is>
+      </c>
+      <c r="B344" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Белфери+109</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>B7902TM</t>
+        </is>
+      </c>
+      <c r="J344" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K344" s="2" t="n">
+        <v>8500</v>
+      </c>
+      <c r="L344" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="M344" s="3" t="n">
+        <v>11.76470588235294</v>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T344" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U344" s="4" t="n">
+        <v>46288.71528399306</v>
+      </c>
+      <c r="V344" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W344" s="4" t="n">
+        <v>46288.71591094907</v>
+      </c>
+      <c r="X344" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y344" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z344" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="345" ht="19.2" customHeight="1">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>20260923-0002</t>
+        </is>
+      </c>
+      <c r="B345" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>НХК-Деветак-Риш-Нова Бяла река</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>ДИРОСИ ООД</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>СТАНИСЛАВ ДИМИТРОВ ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>А5420НХ</t>
+        </is>
+      </c>
+      <c r="J345" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="K345" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L345" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="M345" s="3" t="n">
+        <v>13.33333333333333</v>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P345" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="T345" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U345" s="4" t="n">
+        <v>46288.71627721065</v>
+      </c>
+      <c r="V345" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W345" s="4" t="n">
+        <v>46288.71788559027</v>
+      </c>
+      <c r="X345" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y345" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z345" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="19.2" customHeight="1">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>20260923-0003</t>
+        </is>
+      </c>
+      <c r="B346" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Каварна-Добрич-Терем-Варна</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J346" s="2" t="n">
+        <v>480</v>
+      </c>
+      <c r="K346" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L346" s="2" t="n">
+        <v>576</v>
+      </c>
+      <c r="M346" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="N346" s="2" t="n">
+        <v>14000</v>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P346" s="2" t="n">
+        <v>21000</v>
+      </c>
+      <c r="T346" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U346" s="4" t="n">
+        <v>46288.71793293981</v>
+      </c>
+      <c r="V346" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W346" s="4" t="n">
+        <v>46288.72087140047</v>
+      </c>
+      <c r="X346" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y346" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z346" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="19.2" customHeight="1">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>20260923-0004</t>
+        </is>
+      </c>
+      <c r="B347" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Варна-Любен-Крумово-Сенокос-Варна</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИВАНОВ СТОЯНОВ</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J347" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="K347" s="2" t="n">
+        <v>32500</v>
+      </c>
+      <c r="L347" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="M347" s="3" t="n">
+        <v>5.538461538461538</v>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P347" s="2" t="n">
+        <v>32500</v>
+      </c>
+      <c r="T347" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U347" s="4" t="n">
+        <v>46288.72108383102</v>
+      </c>
+      <c r="V347" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W347" s="4" t="n">
+        <v>46288.7232521875</v>
+      </c>
+      <c r="X347" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y347" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z347" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="348" ht="19.2" customHeight="1">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>20260923-0005</t>
+        </is>
+      </c>
+      <c r="B348" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>НХК-МП Ленд</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>ДИРОСИ ООД</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>СТАНИСЛАВ ДИМИТРОВ ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>А5420НХ</t>
+        </is>
+      </c>
+      <c r="J348" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="K348" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L348" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="M348" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P348" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U348" s="4" t="n">
+        <v>46288.72336778935</v>
+      </c>
+      <c r="V348" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W348" s="4" t="n">
+        <v>46288.72431109954</v>
+      </c>
+      <c r="X348" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y348" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z348" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="349" ht="19.2" customHeight="1">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>20260923-0006</t>
+        </is>
+      </c>
+      <c r="B349" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J349" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="K349" s="2" t="n">
+        <v>36200</v>
+      </c>
+      <c r="L349" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="M349" s="3" t="n">
+        <v>8.618784530386741</v>
+      </c>
+      <c r="N349" s="2" t="n">
+        <v>14000</v>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P349" s="2" t="n">
+        <v>14000</v>
+      </c>
+      <c r="T349" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U349" s="4" t="n">
+        <v>46288.72434427083</v>
+      </c>
+      <c r="V349" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W349" s="4" t="n">
+        <v>46288.72624538194</v>
+      </c>
+      <c r="X349" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y349" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z349" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="350" ht="19.2" customHeight="1">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>20260923-0007</t>
+        </is>
+      </c>
+      <c r="B350" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Курс Живко</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>"СИ-ТРАНС БЪЛГАРИЯ"  ЕООД</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>Живко Демиров Вълчев</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>В9261РА</t>
+        </is>
+      </c>
+      <c r="J350" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="K350" s="2" t="n">
+        <v>3400</v>
+      </c>
+      <c r="L350" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="M350" s="3" t="n">
+        <v>17.64705882352941</v>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P350" s="2" t="n">
+        <v>3400</v>
+      </c>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U350" s="4" t="n">
+        <v>46288.72628569444</v>
+      </c>
+      <c r="V350" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W350" s="4" t="n">
+        <v>46288.72732057871</v>
+      </c>
+      <c r="X350" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y350" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z350" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="351" ht="19.2" customHeight="1">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>20260923-0008</t>
+        </is>
+      </c>
+      <c r="B351" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Каварна-Любен-Варна</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J351" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="K351" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L351" s="2" t="n">
+        <v>540</v>
+      </c>
+      <c r="M351" s="3" t="n">
+        <v>16.875</v>
+      </c>
+      <c r="N351" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P351" s="2" t="n">
+        <v>22000</v>
+      </c>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U351" s="4" t="n">
+        <v>46288.72735028935</v>
+      </c>
+      <c r="V351" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W351" s="4" t="n">
+        <v>46288.72883091436</v>
+      </c>
+      <c r="X351" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y351" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z351" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="352" ht="19.2" customHeight="1">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>20260923-0009</t>
+        </is>
+      </c>
+      <c r="B352" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Русе-Бяла-Копривец-Ушинци-Вълчи дол - Брестак - Добрич-Нова Камена - Северняк-Русе</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="J352" s="2" t="n">
+        <v>620</v>
+      </c>
+      <c r="K352" s="2" t="n">
+        <v>31800</v>
+      </c>
+      <c r="L352" s="2" t="n">
+        <v>744</v>
+      </c>
+      <c r="M352" s="3" t="n">
+        <v>23.39622641509434</v>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P352" s="2" t="n">
+        <v>13500</v>
+      </c>
+      <c r="T352" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U352" s="4" t="n">
+        <v>46288.72886894676</v>
+      </c>
+      <c r="V352" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W352" s="4" t="n">
+        <v>46288.73306398148</v>
+      </c>
+      <c r="X352" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y352" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z352" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="353" ht="19.2" customHeight="1">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>20260923-0010</t>
+        </is>
+      </c>
+      <c r="B353" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Дългопол-Долни Чифлик - Ген Тошево-Добрич-Паскалево-Тервел-Русе</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J353" s="2" t="n">
+        <v>480</v>
+      </c>
+      <c r="K353" s="2" t="n">
+        <v>37000</v>
+      </c>
+      <c r="L353" s="2" t="n">
+        <v>576</v>
+      </c>
+      <c r="M353" s="3" t="n">
+        <v>15.56756756756757</v>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P353" s="2" t="n">
+        <v>37000</v>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U353" s="4" t="n">
+        <v>46288.73310393518</v>
+      </c>
+      <c r="V353" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W353" s="4" t="n">
+        <v>46288.74181456018</v>
+      </c>
+      <c r="X353" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y353" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z353" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="354" ht="19.2" customHeight="1">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>20260923-0011</t>
+        </is>
+      </c>
+      <c r="B354" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Хидро+Мелница</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="J354" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="K354" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L354" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="M354" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P354" s="2" t="n">
+        <v>35000</v>
+      </c>
+      <c r="T354" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U354" s="4" t="n">
+        <v>46288.7457681713</v>
+      </c>
+      <c r="V354" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W354" s="4" t="n">
+        <v>46288.74732299768</v>
+      </c>
+      <c r="X354" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y354" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z354" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="355" ht="19.2" customHeight="1">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>20260923-0012</t>
+        </is>
+      </c>
+      <c r="B355" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Летище Бургас</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="J355" s="2" t="n">
+        <v>340</v>
+      </c>
+      <c r="K355" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L355" s="2" t="n">
+        <v>408</v>
+      </c>
+      <c r="M355" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T355" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U355" s="4" t="n">
+        <v>46288.74707045139</v>
+      </c>
+      <c r="V355" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W355" s="4" t="n">
+        <v>46288.74789638889</v>
+      </c>
+      <c r="X355" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y355" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z355" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="356" ht="19.2" customHeight="1">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>20260923-0013</t>
+        </is>
+      </c>
+      <c r="B356" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>НХК-Добрич-Тервел-Русе</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="J356" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="K356" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L356" s="2" t="n">
+        <v>480</v>
+      </c>
+      <c r="M356" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P356" s="2" t="n">
+        <v>20600</v>
+      </c>
+      <c r="T356" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U356" s="4" t="n">
+        <v>46288.74799921297</v>
+      </c>
+      <c r="V356" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W356" s="4" t="n">
+        <v>46288.75425887731</v>
+      </c>
+      <c r="X356" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y356" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z356" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="357" ht="19.2" customHeight="1">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>20260923-0014</t>
+        </is>
+      </c>
+      <c r="B357" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Варна - Бяла- Енево - Вълчи дол - Варна</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="J357" s="2" t="n">
+        <v>440</v>
+      </c>
+      <c r="K357" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L357" s="2" t="n">
+        <v>528</v>
+      </c>
+      <c r="M357" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P357" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U357" s="4" t="n">
+        <v>46288.75532431713</v>
+      </c>
+      <c r="V357" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W357" s="4" t="n">
+        <v>46288.76314701389</v>
+      </c>
+      <c r="X357" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y357" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z357" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="358" ht="19.2" customHeight="1">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>20260923-0015</t>
+        </is>
+      </c>
+      <c r="B358" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Варна-Бяла-Варна-Каварна-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="J358" s="2" t="n">
+        <v>570</v>
+      </c>
+      <c r="K358" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L358" s="2" t="n">
+        <v>684</v>
+      </c>
+      <c r="M358" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="N358" s="2" t="n">
+        <v>8000</v>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P358" s="2" t="n">
+        <v>21000</v>
+      </c>
+      <c r="T358" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U358" s="4" t="n">
+        <v>46288.76320226852</v>
+      </c>
+      <c r="V358" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W358" s="4" t="n">
+        <v>46288.76549767361</v>
+      </c>
+      <c r="X358" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y358" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z358" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="359" ht="19.2" customHeight="1">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>20260923-0016</t>
+        </is>
+      </c>
+      <c r="B359" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Хидро - Пещерна</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>ГРАНД  ПЕТРОЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="J359" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="K359" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L359" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="M359" s="3" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P359" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="T359" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U359" s="4" t="n">
+        <v>46288.76553940972</v>
+      </c>
+      <c r="V359" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W359" s="4" t="n">
+        <v>46288.76698381944</v>
+      </c>
+      <c r="X359" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y359" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z359" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="360" ht="19.2" customHeight="1">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>20260928-0001</t>
+        </is>
+      </c>
+      <c r="B360" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Бяла-Стражица-Бяла</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="J360" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="K360" s="2" t="n">
+        <v>24000</v>
+      </c>
+      <c r="L360" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="M360" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T360" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U360" s="4" t="n">
+        <v>46293.69814486111</v>
+      </c>
+      <c r="V360" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W360" s="4" t="n">
+        <v>46293.701139375</v>
+      </c>
+      <c r="X360" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y360" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z360" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="361" ht="19.2" customHeight="1">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>20260928-0002</t>
+        </is>
+      </c>
+      <c r="B361" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Варна-Бяла-Карапелит-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="J361" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="K361" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L361" s="2" t="n">
+        <v>540</v>
+      </c>
+      <c r="M361" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P361" s="2" t="n">
+        <v>7500</v>
+      </c>
+      <c r="T361" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U361" s="4" t="n">
+        <v>46293.7012192824</v>
+      </c>
+      <c r="V361" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W361" s="4" t="n">
+        <v>46293.70243686342</v>
+      </c>
+      <c r="X361" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y361" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z361" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="362" ht="19.2" customHeight="1">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>20260928-0003</t>
+        </is>
+      </c>
+      <c r="B362" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Автомагистрали София
+​</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>ГРАНД  ПЕТРОЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="J362" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="K362" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L362" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="M362" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P362" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="T362" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U362" s="4" t="n">
+        <v>46293.7024746875</v>
+      </c>
+      <c r="V362" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W362" s="4" t="n">
+        <v>46293.70352870371</v>
+      </c>
+      <c r="X362" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y362" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z362" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="363" ht="19.2" customHeight="1">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>20260928-0004</t>
+        </is>
+      </c>
+      <c r="B363" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Варна-Ботево-Стожер-Ген Колево- Варна</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="J363" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="K363" s="2" t="n">
+        <v>13000</v>
+      </c>
+      <c r="L363" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="M363" s="3" t="n">
+        <v>11.53846153846154</v>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P363" s="2" t="n">
+        <v>7000</v>
+      </c>
+      <c r="T363" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U363" s="4" t="n">
+        <v>46293.70356755787</v>
+      </c>
+      <c r="V363" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W363" s="4" t="n">
+        <v>46293.70472444445</v>
+      </c>
+      <c r="X363" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y363" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z363" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="364" ht="19.2" customHeight="1">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>20260928-0005</t>
+        </is>
+      </c>
+      <c r="B364" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Пчелник-Каварна-Варна</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИВАНОВ СТОЯНОВ</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="J364" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="K364" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L364" s="2" t="n">
+        <v>540</v>
+      </c>
+      <c r="M364" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="N364" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P364" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="T364" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U364" s="4" t="n">
+        <v>46293.70476439815</v>
+      </c>
+      <c r="V364" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W364" s="4" t="n">
+        <v>46293.7065990625</v>
+      </c>
+      <c r="X364" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y364" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z364" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="365" ht="19.2" customHeight="1">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>20260928-0006</t>
+        </is>
+      </c>
+      <c r="B365" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Русе-Тервел-Русе</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="J365" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="K365" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L365" s="2" t="n">
+        <v>396</v>
+      </c>
+      <c r="M365" s="3" t="n">
+        <v>12.375</v>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P365" s="2" t="n">
+        <v>31000</v>
+      </c>
+      <c r="T365" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U365" s="4" t="n">
+        <v>46293.70663484954</v>
+      </c>
+      <c r="V365" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W365" s="4" t="n">
+        <v>46293.70785103009</v>
+      </c>
+      <c r="X365" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y365" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z365" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="366" ht="19.2" customHeight="1">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>20260928-0007</t>
+        </is>
+      </c>
+      <c r="B366" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Варна-Бяла-Варна</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="J366" s="2" t="n">
+        <v>420</v>
+      </c>
+      <c r="K366" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L366" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="M366" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N366" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P366" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T366" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U366" s="4" t="n">
+        <v>46293.70789803241</v>
+      </c>
+      <c r="V366" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W366" s="4" t="n">
+        <v>46293.70990542824</v>
+      </c>
+      <c r="X366" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y366" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z366" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="367" ht="19.2" customHeight="1">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>20260928-0008</t>
+        </is>
+      </c>
+      <c r="B367" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Русе - Житница-Черна-Нова камена-Русе</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="J367" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="K367" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L367" s="2" t="n">
+        <v>480</v>
+      </c>
+      <c r="M367" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P367" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T367" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U367" s="4" t="n">
+        <v>46293.70994758102</v>
+      </c>
+      <c r="V367" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W367" s="4" t="n">
+        <v>46293.71139060185</v>
+      </c>
+      <c r="X367" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y367" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z367" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="368" ht="19.2" customHeight="1">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>20260928-0009</t>
+        </is>
+      </c>
+      <c r="B368" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Хидро-Варна</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИВАНОВ СТОЯНОВ</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J368" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="K368" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L368" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="M368" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P368" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T368" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U368" s="4" t="n">
+        <v>46293.71144064815</v>
+      </c>
+      <c r="V368" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W368" s="4" t="n">
+        <v>46296.54406861111</v>
+      </c>
+      <c r="X368" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y368" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z368" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="369" ht="19.2" customHeight="1">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>20260928-0010</t>
+        </is>
+      </c>
+      <c r="B369" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Варна-Бяла-Блъсково-Варна</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИВАНОВ СТОЯНОВ</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J369" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="K369" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L369" s="2" t="n">
+        <v>288</v>
+      </c>
+      <c r="M369" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P369" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T369" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U369" s="4" t="n">
+        <v>46293.71249636574</v>
+      </c>
+      <c r="V369" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W369" s="4" t="n">
+        <v>46296.54415320602</v>
+      </c>
+      <c r="X369" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y369" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z369" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="370" ht="19.2" customHeight="1">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>20260928-0011</t>
+        </is>
+      </c>
+      <c r="B370" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Ваарна-Аспарухово-Караманите-Добрич-Малина-Варна</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="J370" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="K370" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L370" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="M370" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P370" s="2" t="n">
+        <v>9500</v>
+      </c>
+      <c r="T370" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U370" s="4" t="n">
+        <v>46293.7138096875</v>
+      </c>
+      <c r="V370" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W370" s="4" t="n">
+        <v>46293.71562453704</v>
+      </c>
+      <c r="X370" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y370" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z370" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="371" ht="19.2" customHeight="1">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>20260928-0012</t>
+        </is>
+      </c>
+      <c r="B371" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Каварна-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИВАНОВ СТОЯНОВ</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J371" s="2" t="n">
+        <v>480</v>
+      </c>
+      <c r="K371" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L371" s="2" t="n">
+        <v>576</v>
+      </c>
+      <c r="M371" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="N371" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P371" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="T371" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U371" s="4" t="n">
+        <v>46293.71581353009</v>
+      </c>
+      <c r="V371" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W371" s="4" t="n">
+        <v>46293.71712799768</v>
+      </c>
+      <c r="X371" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y371" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z371" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/transport/transport_data.xlsx
+++ b/transport/transport_data.xlsx
@@ -24933,10 +24933,10 @@
         <v>18000</v>
       </c>
       <c r="L270" s="2" t="n">
-        <v>3000</v>
+        <v>300</v>
       </c>
       <c r="M270" s="3" t="n">
-        <v>166.6666666666667</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="O270" t="inlineStr">
         <is>
@@ -24956,11 +24956,11 @@
       </c>
       <c r="V270" t="inlineStr">
         <is>
-          <t>Vesela Nikolova</t>
+          <t>Plamen Svetoslavov</t>
         </is>
       </c>
       <c r="W270" s="4" t="n">
-        <v>46240.76312576389</v>
+        <v>46303.68305643518</v>
       </c>
       <c r="X270" t="inlineStr">
         <is>
